--- a/Employee Turnover Analysis Excel Dashboard Dataset.xlsx
+++ b/Employee Turnover Analysis Excel Dashboard Dataset.xlsx
@@ -2,34 +2,35 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30026"/>
-  <workbookPr defaultThemeVersion="124226"/>
+  <workbookPr hidePivotFieldList="1" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\notes\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{174AD653-56B3-4BD0-BE47-52FC83770E1A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39ABD47E-C739-40E3-9615-215997ED9567}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet3" sheetId="3" r:id="rId1"/>
     <sheet name="Sheet1" sheetId="1" r:id="rId2"/>
     <sheet name="dashboard1" sheetId="2" r:id="rId3"/>
+    <sheet name="Sheet4" sheetId="4" r:id="rId4"/>
   </sheets>
   <definedNames>
     <definedName name="datatable">Sheet1!$A$1:$H$101</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="13" r:id="rId4"/>
-    <pivotCache cacheId="19" r:id="rId5"/>
+    <pivotCache cacheId="26" r:id="rId5"/>
+    <pivotCache cacheId="31" r:id="rId6"/>
   </pivotCaches>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="387" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="402" uniqueCount="43">
   <si>
     <t>Employee ID</t>
   </si>
@@ -112,10 +113,16 @@
     <t>Grand Total</t>
   </si>
   <si>
+    <t>Count of Employee ID</t>
+  </si>
+  <si>
     <t>status</t>
   </si>
   <si>
     <t>no of employees</t>
+  </si>
+  <si>
+    <t>Column Labels</t>
   </si>
   <si>
     <t>Employee Status</t>
@@ -124,22 +131,34 @@
     <t>Department wise employee status</t>
   </si>
   <si>
-    <t>agegroup</t>
-  </si>
-  <si>
-    <t>30-40</t>
-  </si>
-  <si>
-    <t>40-50</t>
-  </si>
-  <si>
     <t>50-60</t>
   </si>
   <si>
-    <t>18-30</t>
+    <t>20-29</t>
   </si>
   <si>
-    <t>noofemployee</t>
+    <t>30-39</t>
+  </si>
+  <si>
+    <t>40-49</t>
+  </si>
+  <si>
+    <t>Reason of switch</t>
+  </si>
+  <si>
+    <t>Reason</t>
+  </si>
+  <si>
+    <t>ageGroup</t>
+  </si>
+  <si>
+    <t>age wise record</t>
+  </si>
+  <si>
+    <t>Exited numbers/ gender</t>
+  </si>
+  <si>
+    <t>no of years</t>
   </si>
 </sst>
 </file>
@@ -149,7 +168,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -165,16 +184,30 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="-0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="11">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -198,113 +231,108 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF999999"/>
+      <left style="medium">
+        <color indexed="64"/>
       </left>
       <right/>
-      <top style="thin">
-        <color rgb="FF999999"/>
+      <top style="medium">
+        <color indexed="64"/>
       </top>
       <bottom/>
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color indexed="65"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color rgb="FF999999"/>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
       </top>
       <bottom/>
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color indexed="65"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF999999"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF999999"/>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
       </top>
       <bottom/>
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF999999"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color indexed="65"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="65"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color indexed="65"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="65"/>
+      <left style="medium">
+        <color indexed="64"/>
       </left>
       <right style="thin">
-        <color rgb="FF999999"/>
+        <color auto="1"/>
       </right>
       <top style="thin">
-        <color indexed="65"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF999999"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color indexed="65"/>
+        <color auto="1"/>
       </top>
       <bottom style="thin">
-        <color rgb="FF999999"/>
+        <color auto="1"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left style="thin">
-        <color indexed="65"/>
+        <color auto="1"/>
       </left>
-      <right/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
       <top style="thin">
-        <color indexed="65"/>
+        <color auto="1"/>
       </top>
       <bottom style="thin">
-        <color rgb="FF999999"/>
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left style="thin">
-        <color indexed="65"/>
+        <color auto="1"/>
       </left>
       <right style="thin">
-        <color rgb="FF999999"/>
+        <color auto="1"/>
       </right>
       <top style="thin">
-        <color indexed="65"/>
+        <color auto="1"/>
       </top>
-      <bottom style="thin">
-        <color rgb="FF999999"/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
       </bottom>
       <diagonal/>
     </border>
@@ -312,7 +340,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -323,15 +351,6 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -340,14 +359,771 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" pivotButton="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" pivotButton="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" pivotButton="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="38">
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <bottom style="medium">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <bottom style="medium">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <bottom style="medium">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <bottom style="medium">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <bottom style="medium">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <bottom style="medium">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <bottom style="medium">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <bottom style="medium">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <bottom style="medium">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <bottom style="medium">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top style="medium">
+          <color indexed="64"/>
+        </top>
+        <bottom style="medium">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top style="medium">
+          <color indexed="64"/>
+        </top>
+        <bottom style="medium">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top style="medium">
+          <color indexed="64"/>
+        </top>
+        <bottom style="medium">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -360,8 +1136,2429 @@
 </styleSheet>
 </file>
 
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:pivotSource>
+    <c:name>[Employee Turnover Analysis Excel Dashboard Dataset.xlsx]dashboard1!PivotTable5</c:name>
+    <c:fmtId val="5"/>
+  </c:pivotSource>
+  <c:chart>
+    <c:title>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:pivotFmts>
+      <c:pivotFmt>
+        <c:idx val="0"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="1"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+    </c:pivotFmts>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>dashboard1!$E$3</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Total</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>dashboard1!$D$4:$D$10</c:f>
+              <c:strCache>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>Better Opportunity</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Health Issues</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Personal Reasons</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Relocation</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Retirement</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>Termination</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>dashboard1!$E$4:$E$10</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>8</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-1E5F-4519-B2A4-08C27588F528}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="219"/>
+        <c:overlap val="-27"/>
+        <c:axId val="1451795727"/>
+        <c:axId val="1451781807"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="1451795727"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1451781807"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1451781807"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1451795727"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="tx2">
+        <a:lumMod val="40000"/>
+        <a:lumOff val="60000"/>
+      </a:schemeClr>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="accent1">
+          <a:lumMod val="75000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+  <c:extLst>
+    <c:ext xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" uri="{781A3756-C4B2-4CAC-9D66-4F8BD8637D16}">
+      <c14:pivotOptions>
+        <c14:dropZoneFilter val="1"/>
+        <c14:dropZoneCategories val="1"/>
+        <c14:dropZoneData val="1"/>
+        <c14:dropZoneSeries val="1"/>
+        <c14:dropZonesVisible val="1"/>
+      </c14:pivotOptions>
+    </c:ext>
+    <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{E28EC0CA-F0BB-4C9C-879D-F8772B89E7AC}">
+      <c16:pivotOptions16>
+        <c16:showExpandCollapseFieldButtons val="1"/>
+      </c16:pivotOptions16>
+    </c:ext>
+  </c:extLst>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:pivotSource>
+    <c:name>[Employee Turnover Analysis Excel Dashboard Dataset.xlsx]dashboard1!PivotTable6</c:name>
+    <c:fmtId val="9"/>
+  </c:pivotSource>
+  <c:chart>
+    <c:autoTitleDeleted val="0"/>
+    <c:pivotFmts>
+      <c:pivotFmt>
+        <c:idx val="0"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="1"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln w="28575" cap="rnd">
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="2"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="3"/>
+        <c:spPr>
+          <a:ln w="28575" cap="rnd">
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="4"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent3">
+              <a:lumMod val="75000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+      </c:pivotFmt>
+    </c:pivotFmts>
+    <c:plotArea>
+      <c:layout>
+        <c:manualLayout>
+          <c:layoutTarget val="inner"/>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="5.2692038495188102E-2"/>
+          <c:y val="0.20731262758821814"/>
+          <c:w val="0.73580752405949257"/>
+          <c:h val="0.65853091280256637"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>dashboard1!$E$13:$E$14</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Active</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dPt>
+            <c:idx val="2"/>
+            <c:invertIfNegative val="0"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent3">
+                  <a:lumMod val="75000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000002-9AA9-4AA7-9FAA-FC3F505C72BC}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:cat>
+            <c:strRef>
+              <c:f>dashboard1!$D$15:$D$19</c:f>
+              <c:strCache>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>20-29</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>30-39</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>40-49</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>50-60</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>dashboard1!$E$15:$E$19</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>14</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>14</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>20</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>14</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-9AA9-4AA7-9FAA-FC3F505C72BC}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="150"/>
+        <c:axId val="1451757327"/>
+        <c:axId val="1435022031"/>
+      </c:barChart>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>dashboard1!$F$13:$F$14</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Exited</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>dashboard1!$D$15:$D$19</c:f>
+              <c:strCache>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>20-29</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>30-39</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>40-49</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>50-60</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>dashboard1!$F$15:$F$19</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>14</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>6</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-9AA9-4AA7-9FAA-FC3F505C72BC}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:marker val="1"/>
+        <c:smooth val="0"/>
+        <c:axId val="1451757327"/>
+        <c:axId val="1435022031"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="1451757327"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1435022031"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1435022031"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1451757327"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="tx2">
+        <a:lumMod val="40000"/>
+        <a:lumOff val="60000"/>
+      </a:schemeClr>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+  <c:extLst>
+    <c:ext xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" uri="{781A3756-C4B2-4CAC-9D66-4F8BD8637D16}">
+      <c14:pivotOptions>
+        <c14:dropZoneFilter val="1"/>
+        <c14:dropZoneCategories val="1"/>
+        <c14:dropZoneData val="1"/>
+        <c14:dropZoneSeries val="1"/>
+        <c14:dropZonesVisible val="1"/>
+      </c14:pivotOptions>
+    </c:ext>
+    <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{E28EC0CA-F0BB-4C9C-879D-F8772B89E7AC}">
+      <c16:pivotOptions16>
+        <c16:showExpandCollapseFieldButtons val="1"/>
+      </c16:pivotOptions16>
+    </c:ext>
+  </c:extLst>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="322">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>14287</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>90487</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name="Chart 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1701C174-0EF5-E6D9-C9AD-46050C7F3F39}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>185737</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>71437</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="4" name="Chart 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6B0040D6-0E2E-F1B5-C1CD-1CA19867CE38}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Shalini Rathore" refreshedDate="46190.637872685184" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="100" xr:uid="{C73F9900-B66A-4264-B5EF-E188AA8CB0C2}">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Shalini Rathore" refreshedDate="46190.642789814818" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="100" xr:uid="{6F32462A-95F2-468C-A4EE-E92DA242EC57}">
+  <cacheSource type="worksheet">
+    <worksheetSource name="datatable"/>
+  </cacheSource>
+  <cacheFields count="8">
+    <cacheField name="Employee ID" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="1001" maxValue="1100"/>
+    </cacheField>
+    <cacheField name="Department" numFmtId="0">
+      <sharedItems/>
+    </cacheField>
+    <cacheField name="Join Date" numFmtId="164">
+      <sharedItems containsSemiMixedTypes="0" containsNonDate="0" containsDate="1" containsString="0" minDate="2018-01-23T00:00:00" maxDate="2024-12-07T00:00:00"/>
+    </cacheField>
+    <cacheField name="Exit Date" numFmtId="0">
+      <sharedItems containsNonDate="0" containsDate="1" containsString="0" containsBlank="1" minDate="2020-04-15T00:00:00" maxDate="2024-12-03T00:00:00"/>
+    </cacheField>
+    <cacheField name="Exit Reason" numFmtId="0">
+      <sharedItems containsBlank="1" count="7">
+        <m/>
+        <s v="Better Opportunity"/>
+        <s v="Retirement"/>
+        <s v="Termination"/>
+        <s v="Health Issues"/>
+        <s v="Relocation"/>
+        <s v="Personal Reasons"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="Status" numFmtId="0">
+      <sharedItems count="2">
+        <s v="Active"/>
+        <s v="Exited"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="Gender" numFmtId="0">
+      <sharedItems count="3">
+        <s v="Female"/>
+        <s v="Male"/>
+        <s v="Other"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="Age" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="22" maxValue="53" count="25">
+        <n v="27"/>
+        <n v="22"/>
+        <n v="50"/>
+        <n v="24"/>
+        <n v="28"/>
+        <n v="40"/>
+        <n v="32"/>
+        <n v="36"/>
+        <n v="49"/>
+        <n v="43"/>
+        <n v="42"/>
+        <n v="35"/>
+        <n v="31"/>
+        <n v="51"/>
+        <n v="48"/>
+        <n v="41"/>
+        <n v="52"/>
+        <n v="33"/>
+        <n v="46"/>
+        <n v="53"/>
+        <n v="29"/>
+        <n v="37"/>
+        <n v="23"/>
+        <n v="25"/>
+        <n v="38"/>
+      </sharedItems>
+      <fieldGroup base="7">
+        <rangePr autoStart="0" autoEnd="0" startNum="20" endNum="60" groupInterval="10"/>
+        <groupItems count="6">
+          <s v="&lt;20"/>
+          <s v="20-29"/>
+          <s v="30-39"/>
+          <s v="40-49"/>
+          <s v="50-60"/>
+          <s v="&gt;60"/>
+        </groupItems>
+      </fieldGroup>
+    </cacheField>
+  </cacheFields>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
+      <x14:pivotCacheDefinition/>
+    </ext>
+  </extLst>
+</pivotCacheDefinition>
+</file>
+
+<file path=xl/pivotCache/pivotCacheDefinition2.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Shalini Rathore" refreshedDate="46190.665853935185" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="100" xr:uid="{C73F9900-B66A-4264-B5EF-E188AA8CB0C2}">
   <cacheSource type="worksheet">
     <worksheetSource ref="A1:H101" sheet="Sheet1"/>
   </cacheSource>
@@ -409,80 +3606,1012 @@
 </pivotCacheDefinition>
 </file>
 
-<file path=xl/pivotCache/pivotCacheDefinition2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Shalini Rathore" refreshedDate="46190.642789814818" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="100" xr:uid="{6F32462A-95F2-468C-A4EE-E92DA242EC57}">
-  <cacheSource type="worksheet">
-    <worksheetSource name="datatable"/>
-  </cacheSource>
-  <cacheFields count="8">
-    <cacheField name="Employee ID" numFmtId="0">
-      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="1001" maxValue="1100"/>
-    </cacheField>
-    <cacheField name="Department" numFmtId="0">
-      <sharedItems/>
-    </cacheField>
-    <cacheField name="Join Date" numFmtId="164">
-      <sharedItems containsSemiMixedTypes="0" containsNonDate="0" containsDate="1" containsString="0" minDate="2018-01-23T00:00:00" maxDate="2024-12-07T00:00:00"/>
-    </cacheField>
-    <cacheField name="Exit Date" numFmtId="0">
-      <sharedItems containsNonDate="0" containsDate="1" containsString="0" containsBlank="1" minDate="2020-04-15T00:00:00" maxDate="2024-12-03T00:00:00"/>
-    </cacheField>
-    <cacheField name="Exit Reason" numFmtId="0">
-      <sharedItems containsBlank="1" count="7">
-        <m/>
-        <s v="Better Opportunity"/>
-        <s v="Retirement"/>
-        <s v="Termination"/>
-        <s v="Health Issues"/>
-        <s v="Relocation"/>
-        <s v="Personal Reasons"/>
-      </sharedItems>
-    </cacheField>
-    <cacheField name="Status" numFmtId="0">
-      <sharedItems/>
-    </cacheField>
-    <cacheField name="Gender" numFmtId="0">
-      <sharedItems/>
-    </cacheField>
-    <cacheField name="Age" numFmtId="0">
-      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="22" maxValue="53" count="25">
-        <n v="27"/>
-        <n v="22"/>
-        <n v="50"/>
-        <n v="24"/>
-        <n v="28"/>
-        <n v="40"/>
-        <n v="32"/>
-        <n v="36"/>
-        <n v="49"/>
-        <n v="43"/>
-        <n v="42"/>
-        <n v="35"/>
-        <n v="31"/>
-        <n v="51"/>
-        <n v="48"/>
-        <n v="41"/>
-        <n v="52"/>
-        <n v="33"/>
-        <n v="46"/>
-        <n v="53"/>
-        <n v="29"/>
-        <n v="37"/>
-        <n v="23"/>
-        <n v="25"/>
-        <n v="38"/>
-      </sharedItems>
-    </cacheField>
-  </cacheFields>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
-      <x14:pivotCacheDefinition/>
-    </ext>
-  </extLst>
-</pivotCacheDefinition>
+<file path=xl/pivotCache/pivotCacheRecords1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="100">
+  <r>
+    <n v="1001"/>
+    <s v="IT"/>
+    <d v="2018-11-03T00:00:00"/>
+    <m/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <n v="1002"/>
+    <s v="Customer Support"/>
+    <d v="2020-10-17T00:00:00"/>
+    <m/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <n v="1003"/>
+    <s v="Customer Support"/>
+    <d v="2021-08-15T00:00:00"/>
+    <m/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="1"/>
+    <x v="2"/>
+  </r>
+  <r>
+    <n v="1004"/>
+    <s v="Customer Support"/>
+    <d v="2023-06-10T00:00:00"/>
+    <m/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="1"/>
+    <x v="3"/>
+  </r>
+  <r>
+    <n v="1005"/>
+    <s v="Customer Support"/>
+    <d v="2019-01-14T00:00:00"/>
+    <d v="2021-09-10T00:00:00"/>
+    <x v="1"/>
+    <x v="1"/>
+    <x v="0"/>
+    <x v="2"/>
+  </r>
+  <r>
+    <n v="1006"/>
+    <s v="Marketing"/>
+    <d v="2022-07-07T00:00:00"/>
+    <d v="2023-02-15T00:00:00"/>
+    <x v="2"/>
+    <x v="1"/>
+    <x v="0"/>
+    <x v="4"/>
+  </r>
+  <r>
+    <n v="1007"/>
+    <s v="Finance"/>
+    <d v="2024-06-14T00:00:00"/>
+    <m/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="5"/>
+  </r>
+  <r>
+    <n v="1008"/>
+    <s v="IT"/>
+    <d v="2018-07-23T00:00:00"/>
+    <m/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="2"/>
+    <x v="6"/>
+  </r>
+  <r>
+    <n v="1009"/>
+    <s v="Customer Support"/>
+    <d v="2023-03-02T00:00:00"/>
+    <m/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="2"/>
+    <x v="2"/>
+  </r>
+  <r>
+    <n v="1010"/>
+    <s v="Sales"/>
+    <d v="2024-02-04T00:00:00"/>
+    <m/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="3"/>
+  </r>
+  <r>
+    <n v="1011"/>
+    <s v="HR"/>
+    <d v="2024-07-01T00:00:00"/>
+    <m/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="1"/>
+    <x v="7"/>
+  </r>
+  <r>
+    <n v="1012"/>
+    <s v="Finance"/>
+    <d v="2021-01-31T00:00:00"/>
+    <d v="2024-01-31T00:00:00"/>
+    <x v="2"/>
+    <x v="1"/>
+    <x v="2"/>
+    <x v="8"/>
+  </r>
+  <r>
+    <n v="1013"/>
+    <s v="IT"/>
+    <d v="2018-12-12T00:00:00"/>
+    <d v="2020-04-15T00:00:00"/>
+    <x v="3"/>
+    <x v="1"/>
+    <x v="1"/>
+    <x v="9"/>
+  </r>
+  <r>
+    <n v="1014"/>
+    <s v="Customer Support"/>
+    <d v="2024-01-23T00:00:00"/>
+    <m/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="1"/>
+    <x v="5"/>
+  </r>
+  <r>
+    <n v="1015"/>
+    <s v="Customer Support"/>
+    <d v="2018-01-23T00:00:00"/>
+    <m/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="2"/>
+    <x v="10"/>
+  </r>
+  <r>
+    <n v="1016"/>
+    <s v="IT"/>
+    <d v="2019-09-09T00:00:00"/>
+    <d v="2022-04-26T00:00:00"/>
+    <x v="4"/>
+    <x v="1"/>
+    <x v="2"/>
+    <x v="11"/>
+  </r>
+  <r>
+    <n v="1017"/>
+    <s v="Finance"/>
+    <d v="2019-03-10T00:00:00"/>
+    <d v="2020-10-13T00:00:00"/>
+    <x v="3"/>
+    <x v="1"/>
+    <x v="0"/>
+    <x v="12"/>
+  </r>
+  <r>
+    <n v="1018"/>
+    <s v="HR"/>
+    <d v="2022-02-27T00:00:00"/>
+    <m/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="2"/>
+    <x v="13"/>
+  </r>
+  <r>
+    <n v="1019"/>
+    <s v="IT"/>
+    <d v="2024-07-12T00:00:00"/>
+    <m/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="2"/>
+    <x v="14"/>
+  </r>
+  <r>
+    <n v="1020"/>
+    <s v="Finance"/>
+    <d v="2019-05-03T00:00:00"/>
+    <d v="2022-12-01T00:00:00"/>
+    <x v="5"/>
+    <x v="1"/>
+    <x v="0"/>
+    <x v="15"/>
+  </r>
+  <r>
+    <n v="1021"/>
+    <s v="HR"/>
+    <d v="2021-02-23T00:00:00"/>
+    <d v="2024-04-10T00:00:00"/>
+    <x v="2"/>
+    <x v="1"/>
+    <x v="2"/>
+    <x v="11"/>
+  </r>
+  <r>
+    <n v="1022"/>
+    <s v="Marketing"/>
+    <d v="2023-11-14T00:00:00"/>
+    <d v="2024-06-03T00:00:00"/>
+    <x v="4"/>
+    <x v="1"/>
+    <x v="2"/>
+    <x v="3"/>
+  </r>
+  <r>
+    <n v="1023"/>
+    <s v="Customer Support"/>
+    <d v="2023-11-26T00:00:00"/>
+    <m/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="2"/>
+    <x v="15"/>
+  </r>
+  <r>
+    <n v="1024"/>
+    <s v="Marketing"/>
+    <d v="2024-06-22T00:00:00"/>
+    <m/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="2"/>
+    <x v="5"/>
+  </r>
+  <r>
+    <n v="1025"/>
+    <s v="IT"/>
+    <d v="2019-05-12T00:00:00"/>
+    <m/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="14"/>
+  </r>
+  <r>
+    <n v="1026"/>
+    <s v="Customer Support"/>
+    <d v="2022-11-01T00:00:00"/>
+    <m/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="16"/>
+  </r>
+  <r>
+    <n v="1027"/>
+    <s v="Sales"/>
+    <d v="2020-06-24T00:00:00"/>
+    <d v="2021-09-24T00:00:00"/>
+    <x v="6"/>
+    <x v="1"/>
+    <x v="2"/>
+    <x v="17"/>
+  </r>
+  <r>
+    <n v="1028"/>
+    <s v="Marketing"/>
+    <d v="2023-06-18T00:00:00"/>
+    <m/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="1"/>
+    <x v="13"/>
+  </r>
+  <r>
+    <n v="1029"/>
+    <s v="IT"/>
+    <d v="2021-06-13T00:00:00"/>
+    <d v="2022-07-13T00:00:00"/>
+    <x v="3"/>
+    <x v="1"/>
+    <x v="1"/>
+    <x v="18"/>
+  </r>
+  <r>
+    <n v="1030"/>
+    <s v="Marketing"/>
+    <d v="2018-11-15T00:00:00"/>
+    <d v="2021-04-17T00:00:00"/>
+    <x v="1"/>
+    <x v="1"/>
+    <x v="2"/>
+    <x v="19"/>
+  </r>
+  <r>
+    <n v="1031"/>
+    <s v="HR"/>
+    <d v="2021-02-22T00:00:00"/>
+    <m/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="1"/>
+    <x v="11"/>
+  </r>
+  <r>
+    <n v="1032"/>
+    <s v="IT"/>
+    <d v="2024-08-29T00:00:00"/>
+    <m/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="1"/>
+    <x v="6"/>
+  </r>
+  <r>
+    <n v="1033"/>
+    <s v="HR"/>
+    <d v="2021-06-30T00:00:00"/>
+    <m/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="18"/>
+  </r>
+  <r>
+    <n v="1034"/>
+    <s v="IT"/>
+    <d v="2020-09-14T00:00:00"/>
+    <m/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="1"/>
+    <x v="2"/>
+  </r>
+  <r>
+    <n v="1035"/>
+    <s v="Marketing"/>
+    <d v="2018-09-30T00:00:00"/>
+    <d v="2022-09-21T00:00:00"/>
+    <x v="2"/>
+    <x v="1"/>
+    <x v="1"/>
+    <x v="6"/>
+  </r>
+  <r>
+    <n v="1036"/>
+    <s v="Marketing"/>
+    <d v="2018-08-02T00:00:00"/>
+    <m/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="2"/>
+    <x v="20"/>
+  </r>
+  <r>
+    <n v="1037"/>
+    <s v="Marketing"/>
+    <d v="2021-08-10T00:00:00"/>
+    <d v="2024-12-02T00:00:00"/>
+    <x v="1"/>
+    <x v="1"/>
+    <x v="2"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <n v="1038"/>
+    <s v="Sales"/>
+    <d v="2021-05-08T00:00:00"/>
+    <d v="2023-05-30T00:00:00"/>
+    <x v="4"/>
+    <x v="1"/>
+    <x v="0"/>
+    <x v="12"/>
+  </r>
+  <r>
+    <n v="1039"/>
+    <s v="IT"/>
+    <d v="2019-02-17T00:00:00"/>
+    <d v="2022-12-28T00:00:00"/>
+    <x v="3"/>
+    <x v="1"/>
+    <x v="2"/>
+    <x v="3"/>
+  </r>
+  <r>
+    <n v="1040"/>
+    <s v="HR"/>
+    <d v="2020-12-15T00:00:00"/>
+    <m/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="2"/>
+    <x v="21"/>
+  </r>
+  <r>
+    <n v="1041"/>
+    <s v="Sales"/>
+    <d v="2020-09-25T00:00:00"/>
+    <m/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="22"/>
+  </r>
+  <r>
+    <n v="1042"/>
+    <s v="Sales"/>
+    <d v="2024-12-06T00:00:00"/>
+    <m/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="1"/>
+    <x v="12"/>
+  </r>
+  <r>
+    <n v="1043"/>
+    <s v="HR"/>
+    <d v="2024-01-03T00:00:00"/>
+    <m/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="2"/>
+    <x v="16"/>
+  </r>
+  <r>
+    <n v="1044"/>
+    <s v="Marketing"/>
+    <d v="2022-01-29T00:00:00"/>
+    <m/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="2"/>
+    <x v="23"/>
+  </r>
+  <r>
+    <n v="1045"/>
+    <s v="Customer Support"/>
+    <d v="2023-10-16T00:00:00"/>
+    <m/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="18"/>
+  </r>
+  <r>
+    <n v="1046"/>
+    <s v="Customer Support"/>
+    <d v="2019-06-08T00:00:00"/>
+    <d v="2021-02-01T00:00:00"/>
+    <x v="5"/>
+    <x v="1"/>
+    <x v="2"/>
+    <x v="3"/>
+  </r>
+  <r>
+    <n v="1047"/>
+    <s v="Customer Support"/>
+    <d v="2021-11-14T00:00:00"/>
+    <d v="2024-08-25T00:00:00"/>
+    <x v="5"/>
+    <x v="1"/>
+    <x v="2"/>
+    <x v="24"/>
+  </r>
+  <r>
+    <n v="1048"/>
+    <s v="Finance"/>
+    <d v="2019-08-23T00:00:00"/>
+    <m/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="1"/>
+    <x v="8"/>
+  </r>
+  <r>
+    <n v="1049"/>
+    <s v="Sales"/>
+    <d v="2024-09-05T00:00:00"/>
+    <m/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="1"/>
+    <x v="12"/>
+  </r>
+  <r>
+    <n v="1050"/>
+    <s v="IT"/>
+    <d v="2018-07-16T00:00:00"/>
+    <d v="2022-05-01T00:00:00"/>
+    <x v="4"/>
+    <x v="1"/>
+    <x v="2"/>
+    <x v="13"/>
+  </r>
+  <r>
+    <n v="1051"/>
+    <s v="IT"/>
+    <d v="2018-11-03T00:00:00"/>
+    <m/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <n v="1052"/>
+    <s v="Customer Support"/>
+    <d v="2020-10-17T00:00:00"/>
+    <m/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <n v="1053"/>
+    <s v="Customer Support"/>
+    <d v="2021-08-15T00:00:00"/>
+    <m/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="1"/>
+    <x v="2"/>
+  </r>
+  <r>
+    <n v="1054"/>
+    <s v="Customer Support"/>
+    <d v="2023-06-10T00:00:00"/>
+    <m/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="1"/>
+    <x v="3"/>
+  </r>
+  <r>
+    <n v="1055"/>
+    <s v="Customer Support"/>
+    <d v="2019-01-14T00:00:00"/>
+    <d v="2021-09-10T00:00:00"/>
+    <x v="1"/>
+    <x v="1"/>
+    <x v="0"/>
+    <x v="2"/>
+  </r>
+  <r>
+    <n v="1056"/>
+    <s v="Marketing"/>
+    <d v="2022-07-07T00:00:00"/>
+    <d v="2023-02-15T00:00:00"/>
+    <x v="2"/>
+    <x v="1"/>
+    <x v="0"/>
+    <x v="4"/>
+  </r>
+  <r>
+    <n v="1057"/>
+    <s v="Finance"/>
+    <d v="2024-06-14T00:00:00"/>
+    <m/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="5"/>
+  </r>
+  <r>
+    <n v="1058"/>
+    <s v="IT"/>
+    <d v="2018-07-23T00:00:00"/>
+    <m/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="2"/>
+    <x v="6"/>
+  </r>
+  <r>
+    <n v="1059"/>
+    <s v="Customer Support"/>
+    <d v="2023-03-02T00:00:00"/>
+    <m/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="2"/>
+    <x v="2"/>
+  </r>
+  <r>
+    <n v="1060"/>
+    <s v="Sales"/>
+    <d v="2024-02-04T00:00:00"/>
+    <m/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="3"/>
+  </r>
+  <r>
+    <n v="1061"/>
+    <s v="HR"/>
+    <d v="2024-07-01T00:00:00"/>
+    <m/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="1"/>
+    <x v="7"/>
+  </r>
+  <r>
+    <n v="1062"/>
+    <s v="Finance"/>
+    <d v="2021-01-31T00:00:00"/>
+    <d v="2024-01-31T00:00:00"/>
+    <x v="2"/>
+    <x v="1"/>
+    <x v="2"/>
+    <x v="8"/>
+  </r>
+  <r>
+    <n v="1063"/>
+    <s v="IT"/>
+    <d v="2018-12-12T00:00:00"/>
+    <d v="2020-04-15T00:00:00"/>
+    <x v="3"/>
+    <x v="1"/>
+    <x v="1"/>
+    <x v="9"/>
+  </r>
+  <r>
+    <n v="1064"/>
+    <s v="Customer Support"/>
+    <d v="2024-01-23T00:00:00"/>
+    <m/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="1"/>
+    <x v="5"/>
+  </r>
+  <r>
+    <n v="1065"/>
+    <s v="Customer Support"/>
+    <d v="2018-01-23T00:00:00"/>
+    <m/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="2"/>
+    <x v="10"/>
+  </r>
+  <r>
+    <n v="1066"/>
+    <s v="IT"/>
+    <d v="2019-09-09T00:00:00"/>
+    <d v="2022-04-26T00:00:00"/>
+    <x v="4"/>
+    <x v="1"/>
+    <x v="2"/>
+    <x v="11"/>
+  </r>
+  <r>
+    <n v="1067"/>
+    <s v="Finance"/>
+    <d v="2019-03-10T00:00:00"/>
+    <d v="2020-10-13T00:00:00"/>
+    <x v="3"/>
+    <x v="1"/>
+    <x v="0"/>
+    <x v="12"/>
+  </r>
+  <r>
+    <n v="1068"/>
+    <s v="HR"/>
+    <d v="2022-02-27T00:00:00"/>
+    <m/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="2"/>
+    <x v="13"/>
+  </r>
+  <r>
+    <n v="1069"/>
+    <s v="IT"/>
+    <d v="2024-07-12T00:00:00"/>
+    <m/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="2"/>
+    <x v="14"/>
+  </r>
+  <r>
+    <n v="1070"/>
+    <s v="Finance"/>
+    <d v="2019-05-03T00:00:00"/>
+    <d v="2022-12-01T00:00:00"/>
+    <x v="5"/>
+    <x v="1"/>
+    <x v="0"/>
+    <x v="15"/>
+  </r>
+  <r>
+    <n v="1071"/>
+    <s v="HR"/>
+    <d v="2021-02-23T00:00:00"/>
+    <d v="2024-04-10T00:00:00"/>
+    <x v="2"/>
+    <x v="1"/>
+    <x v="2"/>
+    <x v="11"/>
+  </r>
+  <r>
+    <n v="1072"/>
+    <s v="Marketing"/>
+    <d v="2023-11-14T00:00:00"/>
+    <d v="2024-06-03T00:00:00"/>
+    <x v="4"/>
+    <x v="1"/>
+    <x v="2"/>
+    <x v="3"/>
+  </r>
+  <r>
+    <n v="1073"/>
+    <s v="Customer Support"/>
+    <d v="2023-11-26T00:00:00"/>
+    <m/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="2"/>
+    <x v="15"/>
+  </r>
+  <r>
+    <n v="1074"/>
+    <s v="Marketing"/>
+    <d v="2024-06-22T00:00:00"/>
+    <m/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="2"/>
+    <x v="5"/>
+  </r>
+  <r>
+    <n v="1075"/>
+    <s v="IT"/>
+    <d v="2019-05-12T00:00:00"/>
+    <m/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="14"/>
+  </r>
+  <r>
+    <n v="1076"/>
+    <s v="Customer Support"/>
+    <d v="2022-11-01T00:00:00"/>
+    <m/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="16"/>
+  </r>
+  <r>
+    <n v="1077"/>
+    <s v="Sales"/>
+    <d v="2020-06-24T00:00:00"/>
+    <d v="2021-09-24T00:00:00"/>
+    <x v="6"/>
+    <x v="1"/>
+    <x v="2"/>
+    <x v="17"/>
+  </r>
+  <r>
+    <n v="1078"/>
+    <s v="Marketing"/>
+    <d v="2023-06-18T00:00:00"/>
+    <m/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="1"/>
+    <x v="13"/>
+  </r>
+  <r>
+    <n v="1079"/>
+    <s v="IT"/>
+    <d v="2021-06-13T00:00:00"/>
+    <d v="2022-07-13T00:00:00"/>
+    <x v="3"/>
+    <x v="1"/>
+    <x v="1"/>
+    <x v="18"/>
+  </r>
+  <r>
+    <n v="1080"/>
+    <s v="Marketing"/>
+    <d v="2018-11-15T00:00:00"/>
+    <d v="2021-04-17T00:00:00"/>
+    <x v="1"/>
+    <x v="1"/>
+    <x v="2"/>
+    <x v="19"/>
+  </r>
+  <r>
+    <n v="1081"/>
+    <s v="HR"/>
+    <d v="2021-02-22T00:00:00"/>
+    <m/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="1"/>
+    <x v="11"/>
+  </r>
+  <r>
+    <n v="1082"/>
+    <s v="IT"/>
+    <d v="2024-08-29T00:00:00"/>
+    <m/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="1"/>
+    <x v="6"/>
+  </r>
+  <r>
+    <n v="1083"/>
+    <s v="HR"/>
+    <d v="2021-06-30T00:00:00"/>
+    <m/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="18"/>
+  </r>
+  <r>
+    <n v="1084"/>
+    <s v="IT"/>
+    <d v="2020-09-14T00:00:00"/>
+    <m/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="1"/>
+    <x v="2"/>
+  </r>
+  <r>
+    <n v="1085"/>
+    <s v="Marketing"/>
+    <d v="2018-09-30T00:00:00"/>
+    <d v="2022-09-21T00:00:00"/>
+    <x v="2"/>
+    <x v="1"/>
+    <x v="1"/>
+    <x v="6"/>
+  </r>
+  <r>
+    <n v="1086"/>
+    <s v="Marketing"/>
+    <d v="2018-08-02T00:00:00"/>
+    <m/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="2"/>
+    <x v="20"/>
+  </r>
+  <r>
+    <n v="1087"/>
+    <s v="Marketing"/>
+    <d v="2021-08-10T00:00:00"/>
+    <d v="2024-12-02T00:00:00"/>
+    <x v="1"/>
+    <x v="1"/>
+    <x v="2"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <n v="1088"/>
+    <s v="Sales"/>
+    <d v="2021-05-08T00:00:00"/>
+    <d v="2023-05-30T00:00:00"/>
+    <x v="4"/>
+    <x v="1"/>
+    <x v="0"/>
+    <x v="12"/>
+  </r>
+  <r>
+    <n v="1089"/>
+    <s v="IT"/>
+    <d v="2019-02-17T00:00:00"/>
+    <d v="2022-12-28T00:00:00"/>
+    <x v="3"/>
+    <x v="1"/>
+    <x v="2"/>
+    <x v="3"/>
+  </r>
+  <r>
+    <n v="1090"/>
+    <s v="HR"/>
+    <d v="2020-12-15T00:00:00"/>
+    <m/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="2"/>
+    <x v="21"/>
+  </r>
+  <r>
+    <n v="1091"/>
+    <s v="Sales"/>
+    <d v="2020-09-25T00:00:00"/>
+    <m/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="22"/>
+  </r>
+  <r>
+    <n v="1092"/>
+    <s v="Sales"/>
+    <d v="2024-12-06T00:00:00"/>
+    <m/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="1"/>
+    <x v="12"/>
+  </r>
+  <r>
+    <n v="1093"/>
+    <s v="HR"/>
+    <d v="2024-01-03T00:00:00"/>
+    <m/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="2"/>
+    <x v="16"/>
+  </r>
+  <r>
+    <n v="1094"/>
+    <s v="Marketing"/>
+    <d v="2022-01-29T00:00:00"/>
+    <m/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="2"/>
+    <x v="23"/>
+  </r>
+  <r>
+    <n v="1095"/>
+    <s v="Customer Support"/>
+    <d v="2023-10-16T00:00:00"/>
+    <m/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="18"/>
+  </r>
+  <r>
+    <n v="1096"/>
+    <s v="Customer Support"/>
+    <d v="2019-06-08T00:00:00"/>
+    <d v="2021-02-01T00:00:00"/>
+    <x v="5"/>
+    <x v="1"/>
+    <x v="2"/>
+    <x v="3"/>
+  </r>
+  <r>
+    <n v="1097"/>
+    <s v="Customer Support"/>
+    <d v="2021-11-14T00:00:00"/>
+    <d v="2024-08-25T00:00:00"/>
+    <x v="5"/>
+    <x v="1"/>
+    <x v="2"/>
+    <x v="24"/>
+  </r>
+  <r>
+    <n v="1098"/>
+    <s v="Finance"/>
+    <d v="2019-08-23T00:00:00"/>
+    <m/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="1"/>
+    <x v="8"/>
+  </r>
+  <r>
+    <n v="1099"/>
+    <s v="Sales"/>
+    <d v="2024-09-05T00:00:00"/>
+    <m/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="1"/>
+    <x v="12"/>
+  </r>
+  <r>
+    <n v="1100"/>
+    <s v="IT"/>
+    <d v="2018-07-16T00:00:00"/>
+    <d v="2022-05-01T00:00:00"/>
+    <x v="4"/>
+    <x v="1"/>
+    <x v="2"/>
+    <x v="13"/>
+  </r>
+</pivotCacheRecords>
 </file>
 
-<file path=xl/pivotCache/pivotCacheRecords1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/pivotCache/pivotCacheRecords2.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="100">
   <r>
     <n v="1001"/>
@@ -1487,1024 +5616,82 @@
 </pivotCacheRecords>
 </file>
 
-<file path=xl/pivotCache/pivotCacheRecords2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="100">
-  <r>
-    <n v="1001"/>
-    <s v="IT"/>
-    <d v="2018-11-03T00:00:00"/>
-    <m/>
-    <x v="0"/>
-    <s v="Active"/>
-    <s v="Female"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <n v="1002"/>
-    <s v="Customer Support"/>
-    <d v="2020-10-17T00:00:00"/>
-    <m/>
-    <x v="0"/>
-    <s v="Active"/>
-    <s v="Female"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <n v="1003"/>
-    <s v="Customer Support"/>
-    <d v="2021-08-15T00:00:00"/>
-    <m/>
-    <x v="0"/>
-    <s v="Active"/>
-    <s v="Male"/>
-    <x v="2"/>
-  </r>
-  <r>
-    <n v="1004"/>
-    <s v="Customer Support"/>
-    <d v="2023-06-10T00:00:00"/>
-    <m/>
-    <x v="0"/>
-    <s v="Active"/>
-    <s v="Male"/>
-    <x v="3"/>
-  </r>
-  <r>
-    <n v="1005"/>
-    <s v="Customer Support"/>
-    <d v="2019-01-14T00:00:00"/>
-    <d v="2021-09-10T00:00:00"/>
-    <x v="1"/>
-    <s v="Exited"/>
-    <s v="Female"/>
-    <x v="2"/>
-  </r>
-  <r>
-    <n v="1006"/>
-    <s v="Marketing"/>
-    <d v="2022-07-07T00:00:00"/>
-    <d v="2023-02-15T00:00:00"/>
-    <x v="2"/>
-    <s v="Exited"/>
-    <s v="Female"/>
-    <x v="4"/>
-  </r>
-  <r>
-    <n v="1007"/>
-    <s v="Finance"/>
-    <d v="2024-06-14T00:00:00"/>
-    <m/>
-    <x v="0"/>
-    <s v="Active"/>
-    <s v="Female"/>
-    <x v="5"/>
-  </r>
-  <r>
-    <n v="1008"/>
-    <s v="IT"/>
-    <d v="2018-07-23T00:00:00"/>
-    <m/>
-    <x v="0"/>
-    <s v="Active"/>
-    <s v="Other"/>
-    <x v="6"/>
-  </r>
-  <r>
-    <n v="1009"/>
-    <s v="Customer Support"/>
-    <d v="2023-03-02T00:00:00"/>
-    <m/>
-    <x v="0"/>
-    <s v="Active"/>
-    <s v="Other"/>
-    <x v="2"/>
-  </r>
-  <r>
-    <n v="1010"/>
-    <s v="Sales"/>
-    <d v="2024-02-04T00:00:00"/>
-    <m/>
-    <x v="0"/>
-    <s v="Active"/>
-    <s v="Female"/>
-    <x v="3"/>
-  </r>
-  <r>
-    <n v="1011"/>
-    <s v="HR"/>
-    <d v="2024-07-01T00:00:00"/>
-    <m/>
-    <x v="0"/>
-    <s v="Active"/>
-    <s v="Male"/>
-    <x v="7"/>
-  </r>
-  <r>
-    <n v="1012"/>
-    <s v="Finance"/>
-    <d v="2021-01-31T00:00:00"/>
-    <d v="2024-01-31T00:00:00"/>
-    <x v="2"/>
-    <s v="Exited"/>
-    <s v="Other"/>
-    <x v="8"/>
-  </r>
-  <r>
-    <n v="1013"/>
-    <s v="IT"/>
-    <d v="2018-12-12T00:00:00"/>
-    <d v="2020-04-15T00:00:00"/>
-    <x v="3"/>
-    <s v="Exited"/>
-    <s v="Male"/>
-    <x v="9"/>
-  </r>
-  <r>
-    <n v="1014"/>
-    <s v="Customer Support"/>
-    <d v="2024-01-23T00:00:00"/>
-    <m/>
-    <x v="0"/>
-    <s v="Active"/>
-    <s v="Male"/>
-    <x v="5"/>
-  </r>
-  <r>
-    <n v="1015"/>
-    <s v="Customer Support"/>
-    <d v="2018-01-23T00:00:00"/>
-    <m/>
-    <x v="0"/>
-    <s v="Active"/>
-    <s v="Other"/>
-    <x v="10"/>
-  </r>
-  <r>
-    <n v="1016"/>
-    <s v="IT"/>
-    <d v="2019-09-09T00:00:00"/>
-    <d v="2022-04-26T00:00:00"/>
-    <x v="4"/>
-    <s v="Exited"/>
-    <s v="Other"/>
-    <x v="11"/>
-  </r>
-  <r>
-    <n v="1017"/>
-    <s v="Finance"/>
-    <d v="2019-03-10T00:00:00"/>
-    <d v="2020-10-13T00:00:00"/>
-    <x v="3"/>
-    <s v="Exited"/>
-    <s v="Female"/>
-    <x v="12"/>
-  </r>
-  <r>
-    <n v="1018"/>
-    <s v="HR"/>
-    <d v="2022-02-27T00:00:00"/>
-    <m/>
-    <x v="0"/>
-    <s v="Active"/>
-    <s v="Other"/>
-    <x v="13"/>
-  </r>
-  <r>
-    <n v="1019"/>
-    <s v="IT"/>
-    <d v="2024-07-12T00:00:00"/>
-    <m/>
-    <x v="0"/>
-    <s v="Active"/>
-    <s v="Other"/>
-    <x v="14"/>
-  </r>
-  <r>
-    <n v="1020"/>
-    <s v="Finance"/>
-    <d v="2019-05-03T00:00:00"/>
-    <d v="2022-12-01T00:00:00"/>
-    <x v="5"/>
-    <s v="Exited"/>
-    <s v="Female"/>
-    <x v="15"/>
-  </r>
-  <r>
-    <n v="1021"/>
-    <s v="HR"/>
-    <d v="2021-02-23T00:00:00"/>
-    <d v="2024-04-10T00:00:00"/>
-    <x v="2"/>
-    <s v="Exited"/>
-    <s v="Other"/>
-    <x v="11"/>
-  </r>
-  <r>
-    <n v="1022"/>
-    <s v="Marketing"/>
-    <d v="2023-11-14T00:00:00"/>
-    <d v="2024-06-03T00:00:00"/>
-    <x v="4"/>
-    <s v="Exited"/>
-    <s v="Other"/>
-    <x v="3"/>
-  </r>
-  <r>
-    <n v="1023"/>
-    <s v="Customer Support"/>
-    <d v="2023-11-26T00:00:00"/>
-    <m/>
-    <x v="0"/>
-    <s v="Active"/>
-    <s v="Other"/>
-    <x v="15"/>
-  </r>
-  <r>
-    <n v="1024"/>
-    <s v="Marketing"/>
-    <d v="2024-06-22T00:00:00"/>
-    <m/>
-    <x v="0"/>
-    <s v="Active"/>
-    <s v="Other"/>
-    <x v="5"/>
-  </r>
-  <r>
-    <n v="1025"/>
-    <s v="IT"/>
-    <d v="2019-05-12T00:00:00"/>
-    <m/>
-    <x v="0"/>
-    <s v="Active"/>
-    <s v="Female"/>
-    <x v="14"/>
-  </r>
-  <r>
-    <n v="1026"/>
-    <s v="Customer Support"/>
-    <d v="2022-11-01T00:00:00"/>
-    <m/>
-    <x v="0"/>
-    <s v="Active"/>
-    <s v="Female"/>
-    <x v="16"/>
-  </r>
-  <r>
-    <n v="1027"/>
-    <s v="Sales"/>
-    <d v="2020-06-24T00:00:00"/>
-    <d v="2021-09-24T00:00:00"/>
-    <x v="6"/>
-    <s v="Exited"/>
-    <s v="Other"/>
-    <x v="17"/>
-  </r>
-  <r>
-    <n v="1028"/>
-    <s v="Marketing"/>
-    <d v="2023-06-18T00:00:00"/>
-    <m/>
-    <x v="0"/>
-    <s v="Active"/>
-    <s v="Male"/>
-    <x v="13"/>
-  </r>
-  <r>
-    <n v="1029"/>
-    <s v="IT"/>
-    <d v="2021-06-13T00:00:00"/>
-    <d v="2022-07-13T00:00:00"/>
-    <x v="3"/>
-    <s v="Exited"/>
-    <s v="Male"/>
-    <x v="18"/>
-  </r>
-  <r>
-    <n v="1030"/>
-    <s v="Marketing"/>
-    <d v="2018-11-15T00:00:00"/>
-    <d v="2021-04-17T00:00:00"/>
-    <x v="1"/>
-    <s v="Exited"/>
-    <s v="Other"/>
-    <x v="19"/>
-  </r>
-  <r>
-    <n v="1031"/>
-    <s v="HR"/>
-    <d v="2021-02-22T00:00:00"/>
-    <m/>
-    <x v="0"/>
-    <s v="Active"/>
-    <s v="Male"/>
-    <x v="11"/>
-  </r>
-  <r>
-    <n v="1032"/>
-    <s v="IT"/>
-    <d v="2024-08-29T00:00:00"/>
-    <m/>
-    <x v="0"/>
-    <s v="Active"/>
-    <s v="Male"/>
-    <x v="6"/>
-  </r>
-  <r>
-    <n v="1033"/>
-    <s v="HR"/>
-    <d v="2021-06-30T00:00:00"/>
-    <m/>
-    <x v="0"/>
-    <s v="Active"/>
-    <s v="Female"/>
-    <x v="18"/>
-  </r>
-  <r>
-    <n v="1034"/>
-    <s v="IT"/>
-    <d v="2020-09-14T00:00:00"/>
-    <m/>
-    <x v="0"/>
-    <s v="Active"/>
-    <s v="Male"/>
-    <x v="2"/>
-  </r>
-  <r>
-    <n v="1035"/>
-    <s v="Marketing"/>
-    <d v="2018-09-30T00:00:00"/>
-    <d v="2022-09-21T00:00:00"/>
-    <x v="2"/>
-    <s v="Exited"/>
-    <s v="Male"/>
-    <x v="6"/>
-  </r>
-  <r>
-    <n v="1036"/>
-    <s v="Marketing"/>
-    <d v="2018-08-02T00:00:00"/>
-    <m/>
-    <x v="0"/>
-    <s v="Active"/>
-    <s v="Other"/>
-    <x v="20"/>
-  </r>
-  <r>
-    <n v="1037"/>
-    <s v="Marketing"/>
-    <d v="2021-08-10T00:00:00"/>
-    <d v="2024-12-02T00:00:00"/>
-    <x v="1"/>
-    <s v="Exited"/>
-    <s v="Other"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <n v="1038"/>
-    <s v="Sales"/>
-    <d v="2021-05-08T00:00:00"/>
-    <d v="2023-05-30T00:00:00"/>
-    <x v="4"/>
-    <s v="Exited"/>
-    <s v="Female"/>
-    <x v="12"/>
-  </r>
-  <r>
-    <n v="1039"/>
-    <s v="IT"/>
-    <d v="2019-02-17T00:00:00"/>
-    <d v="2022-12-28T00:00:00"/>
-    <x v="3"/>
-    <s v="Exited"/>
-    <s v="Other"/>
-    <x v="3"/>
-  </r>
-  <r>
-    <n v="1040"/>
-    <s v="HR"/>
-    <d v="2020-12-15T00:00:00"/>
-    <m/>
-    <x v="0"/>
-    <s v="Active"/>
-    <s v="Other"/>
-    <x v="21"/>
-  </r>
-  <r>
-    <n v="1041"/>
-    <s v="Sales"/>
-    <d v="2020-09-25T00:00:00"/>
-    <m/>
-    <x v="0"/>
-    <s v="Active"/>
-    <s v="Female"/>
-    <x v="22"/>
-  </r>
-  <r>
-    <n v="1042"/>
-    <s v="Sales"/>
-    <d v="2024-12-06T00:00:00"/>
-    <m/>
-    <x v="0"/>
-    <s v="Active"/>
-    <s v="Male"/>
-    <x v="12"/>
-  </r>
-  <r>
-    <n v="1043"/>
-    <s v="HR"/>
-    <d v="2024-01-03T00:00:00"/>
-    <m/>
-    <x v="0"/>
-    <s v="Active"/>
-    <s v="Other"/>
-    <x v="16"/>
-  </r>
-  <r>
-    <n v="1044"/>
-    <s v="Marketing"/>
-    <d v="2022-01-29T00:00:00"/>
-    <m/>
-    <x v="0"/>
-    <s v="Active"/>
-    <s v="Other"/>
-    <x v="23"/>
-  </r>
-  <r>
-    <n v="1045"/>
-    <s v="Customer Support"/>
-    <d v="2023-10-16T00:00:00"/>
-    <m/>
-    <x v="0"/>
-    <s v="Active"/>
-    <s v="Female"/>
-    <x v="18"/>
-  </r>
-  <r>
-    <n v="1046"/>
-    <s v="Customer Support"/>
-    <d v="2019-06-08T00:00:00"/>
-    <d v="2021-02-01T00:00:00"/>
-    <x v="5"/>
-    <s v="Exited"/>
-    <s v="Other"/>
-    <x v="3"/>
-  </r>
-  <r>
-    <n v="1047"/>
-    <s v="Customer Support"/>
-    <d v="2021-11-14T00:00:00"/>
-    <d v="2024-08-25T00:00:00"/>
-    <x v="5"/>
-    <s v="Exited"/>
-    <s v="Other"/>
-    <x v="24"/>
-  </r>
-  <r>
-    <n v="1048"/>
-    <s v="Finance"/>
-    <d v="2019-08-23T00:00:00"/>
-    <m/>
-    <x v="0"/>
-    <s v="Active"/>
-    <s v="Male"/>
-    <x v="8"/>
-  </r>
-  <r>
-    <n v="1049"/>
-    <s v="Sales"/>
-    <d v="2024-09-05T00:00:00"/>
-    <m/>
-    <x v="0"/>
-    <s v="Active"/>
-    <s v="Male"/>
-    <x v="12"/>
-  </r>
-  <r>
-    <n v="1050"/>
-    <s v="IT"/>
-    <d v="2018-07-16T00:00:00"/>
-    <d v="2022-05-01T00:00:00"/>
-    <x v="4"/>
-    <s v="Exited"/>
-    <s v="Other"/>
-    <x v="13"/>
-  </r>
-  <r>
-    <n v="1051"/>
-    <s v="IT"/>
-    <d v="2018-11-03T00:00:00"/>
-    <m/>
-    <x v="0"/>
-    <s v="Active"/>
-    <s v="Female"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <n v="1052"/>
-    <s v="Customer Support"/>
-    <d v="2020-10-17T00:00:00"/>
-    <m/>
-    <x v="0"/>
-    <s v="Active"/>
-    <s v="Female"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <n v="1053"/>
-    <s v="Customer Support"/>
-    <d v="2021-08-15T00:00:00"/>
-    <m/>
-    <x v="0"/>
-    <s v="Active"/>
-    <s v="Male"/>
-    <x v="2"/>
-  </r>
-  <r>
-    <n v="1054"/>
-    <s v="Customer Support"/>
-    <d v="2023-06-10T00:00:00"/>
-    <m/>
-    <x v="0"/>
-    <s v="Active"/>
-    <s v="Male"/>
-    <x v="3"/>
-  </r>
-  <r>
-    <n v="1055"/>
-    <s v="Customer Support"/>
-    <d v="2019-01-14T00:00:00"/>
-    <d v="2021-09-10T00:00:00"/>
-    <x v="1"/>
-    <s v="Exited"/>
-    <s v="Female"/>
-    <x v="2"/>
-  </r>
-  <r>
-    <n v="1056"/>
-    <s v="Marketing"/>
-    <d v="2022-07-07T00:00:00"/>
-    <d v="2023-02-15T00:00:00"/>
-    <x v="2"/>
-    <s v="Exited"/>
-    <s v="Female"/>
-    <x v="4"/>
-  </r>
-  <r>
-    <n v="1057"/>
-    <s v="Finance"/>
-    <d v="2024-06-14T00:00:00"/>
-    <m/>
-    <x v="0"/>
-    <s v="Active"/>
-    <s v="Female"/>
-    <x v="5"/>
-  </r>
-  <r>
-    <n v="1058"/>
-    <s v="IT"/>
-    <d v="2018-07-23T00:00:00"/>
-    <m/>
-    <x v="0"/>
-    <s v="Active"/>
-    <s v="Other"/>
-    <x v="6"/>
-  </r>
-  <r>
-    <n v="1059"/>
-    <s v="Customer Support"/>
-    <d v="2023-03-02T00:00:00"/>
-    <m/>
-    <x v="0"/>
-    <s v="Active"/>
-    <s v="Other"/>
-    <x v="2"/>
-  </r>
-  <r>
-    <n v="1060"/>
-    <s v="Sales"/>
-    <d v="2024-02-04T00:00:00"/>
-    <m/>
-    <x v="0"/>
-    <s v="Active"/>
-    <s v="Female"/>
-    <x v="3"/>
-  </r>
-  <r>
-    <n v="1061"/>
-    <s v="HR"/>
-    <d v="2024-07-01T00:00:00"/>
-    <m/>
-    <x v="0"/>
-    <s v="Active"/>
-    <s v="Male"/>
-    <x v="7"/>
-  </r>
-  <r>
-    <n v="1062"/>
-    <s v="Finance"/>
-    <d v="2021-01-31T00:00:00"/>
-    <d v="2024-01-31T00:00:00"/>
-    <x v="2"/>
-    <s v="Exited"/>
-    <s v="Other"/>
-    <x v="8"/>
-  </r>
-  <r>
-    <n v="1063"/>
-    <s v="IT"/>
-    <d v="2018-12-12T00:00:00"/>
-    <d v="2020-04-15T00:00:00"/>
-    <x v="3"/>
-    <s v="Exited"/>
-    <s v="Male"/>
-    <x v="9"/>
-  </r>
-  <r>
-    <n v="1064"/>
-    <s v="Customer Support"/>
-    <d v="2024-01-23T00:00:00"/>
-    <m/>
-    <x v="0"/>
-    <s v="Active"/>
-    <s v="Male"/>
-    <x v="5"/>
-  </r>
-  <r>
-    <n v="1065"/>
-    <s v="Customer Support"/>
-    <d v="2018-01-23T00:00:00"/>
-    <m/>
-    <x v="0"/>
-    <s v="Active"/>
-    <s v="Other"/>
-    <x v="10"/>
-  </r>
-  <r>
-    <n v="1066"/>
-    <s v="IT"/>
-    <d v="2019-09-09T00:00:00"/>
-    <d v="2022-04-26T00:00:00"/>
-    <x v="4"/>
-    <s v="Exited"/>
-    <s v="Other"/>
-    <x v="11"/>
-  </r>
-  <r>
-    <n v="1067"/>
-    <s v="Finance"/>
-    <d v="2019-03-10T00:00:00"/>
-    <d v="2020-10-13T00:00:00"/>
-    <x v="3"/>
-    <s v="Exited"/>
-    <s v="Female"/>
-    <x v="12"/>
-  </r>
-  <r>
-    <n v="1068"/>
-    <s v="HR"/>
-    <d v="2022-02-27T00:00:00"/>
-    <m/>
-    <x v="0"/>
-    <s v="Active"/>
-    <s v="Other"/>
-    <x v="13"/>
-  </r>
-  <r>
-    <n v="1069"/>
-    <s v="IT"/>
-    <d v="2024-07-12T00:00:00"/>
-    <m/>
-    <x v="0"/>
-    <s v="Active"/>
-    <s v="Other"/>
-    <x v="14"/>
-  </r>
-  <r>
-    <n v="1070"/>
-    <s v="Finance"/>
-    <d v="2019-05-03T00:00:00"/>
-    <d v="2022-12-01T00:00:00"/>
-    <x v="5"/>
-    <s v="Exited"/>
-    <s v="Female"/>
-    <x v="15"/>
-  </r>
-  <r>
-    <n v="1071"/>
-    <s v="HR"/>
-    <d v="2021-02-23T00:00:00"/>
-    <d v="2024-04-10T00:00:00"/>
-    <x v="2"/>
-    <s v="Exited"/>
-    <s v="Other"/>
-    <x v="11"/>
-  </r>
-  <r>
-    <n v="1072"/>
-    <s v="Marketing"/>
-    <d v="2023-11-14T00:00:00"/>
-    <d v="2024-06-03T00:00:00"/>
-    <x v="4"/>
-    <s v="Exited"/>
-    <s v="Other"/>
-    <x v="3"/>
-  </r>
-  <r>
-    <n v="1073"/>
-    <s v="Customer Support"/>
-    <d v="2023-11-26T00:00:00"/>
-    <m/>
-    <x v="0"/>
-    <s v="Active"/>
-    <s v="Other"/>
-    <x v="15"/>
-  </r>
-  <r>
-    <n v="1074"/>
-    <s v="Marketing"/>
-    <d v="2024-06-22T00:00:00"/>
-    <m/>
-    <x v="0"/>
-    <s v="Active"/>
-    <s v="Other"/>
-    <x v="5"/>
-  </r>
-  <r>
-    <n v="1075"/>
-    <s v="IT"/>
-    <d v="2019-05-12T00:00:00"/>
-    <m/>
-    <x v="0"/>
-    <s v="Active"/>
-    <s v="Female"/>
-    <x v="14"/>
-  </r>
-  <r>
-    <n v="1076"/>
-    <s v="Customer Support"/>
-    <d v="2022-11-01T00:00:00"/>
-    <m/>
-    <x v="0"/>
-    <s v="Active"/>
-    <s v="Female"/>
-    <x v="16"/>
-  </r>
-  <r>
-    <n v="1077"/>
-    <s v="Sales"/>
-    <d v="2020-06-24T00:00:00"/>
-    <d v="2021-09-24T00:00:00"/>
-    <x v="6"/>
-    <s v="Exited"/>
-    <s v="Other"/>
-    <x v="17"/>
-  </r>
-  <r>
-    <n v="1078"/>
-    <s v="Marketing"/>
-    <d v="2023-06-18T00:00:00"/>
-    <m/>
-    <x v="0"/>
-    <s v="Active"/>
-    <s v="Male"/>
-    <x v="13"/>
-  </r>
-  <r>
-    <n v="1079"/>
-    <s v="IT"/>
-    <d v="2021-06-13T00:00:00"/>
-    <d v="2022-07-13T00:00:00"/>
-    <x v="3"/>
-    <s v="Exited"/>
-    <s v="Male"/>
-    <x v="18"/>
-  </r>
-  <r>
-    <n v="1080"/>
-    <s v="Marketing"/>
-    <d v="2018-11-15T00:00:00"/>
-    <d v="2021-04-17T00:00:00"/>
-    <x v="1"/>
-    <s v="Exited"/>
-    <s v="Other"/>
-    <x v="19"/>
-  </r>
-  <r>
-    <n v="1081"/>
-    <s v="HR"/>
-    <d v="2021-02-22T00:00:00"/>
-    <m/>
-    <x v="0"/>
-    <s v="Active"/>
-    <s v="Male"/>
-    <x v="11"/>
-  </r>
-  <r>
-    <n v="1082"/>
-    <s v="IT"/>
-    <d v="2024-08-29T00:00:00"/>
-    <m/>
-    <x v="0"/>
-    <s v="Active"/>
-    <s v="Male"/>
-    <x v="6"/>
-  </r>
-  <r>
-    <n v="1083"/>
-    <s v="HR"/>
-    <d v="2021-06-30T00:00:00"/>
-    <m/>
-    <x v="0"/>
-    <s v="Active"/>
-    <s v="Female"/>
-    <x v="18"/>
-  </r>
-  <r>
-    <n v="1084"/>
-    <s v="IT"/>
-    <d v="2020-09-14T00:00:00"/>
-    <m/>
-    <x v="0"/>
-    <s v="Active"/>
-    <s v="Male"/>
-    <x v="2"/>
-  </r>
-  <r>
-    <n v="1085"/>
-    <s v="Marketing"/>
-    <d v="2018-09-30T00:00:00"/>
-    <d v="2022-09-21T00:00:00"/>
-    <x v="2"/>
-    <s v="Exited"/>
-    <s v="Male"/>
-    <x v="6"/>
-  </r>
-  <r>
-    <n v="1086"/>
-    <s v="Marketing"/>
-    <d v="2018-08-02T00:00:00"/>
-    <m/>
-    <x v="0"/>
-    <s v="Active"/>
-    <s v="Other"/>
-    <x v="20"/>
-  </r>
-  <r>
-    <n v="1087"/>
-    <s v="Marketing"/>
-    <d v="2021-08-10T00:00:00"/>
-    <d v="2024-12-02T00:00:00"/>
-    <x v="1"/>
-    <s v="Exited"/>
-    <s v="Other"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <n v="1088"/>
-    <s v="Sales"/>
-    <d v="2021-05-08T00:00:00"/>
-    <d v="2023-05-30T00:00:00"/>
-    <x v="4"/>
-    <s v="Exited"/>
-    <s v="Female"/>
-    <x v="12"/>
-  </r>
-  <r>
-    <n v="1089"/>
-    <s v="IT"/>
-    <d v="2019-02-17T00:00:00"/>
-    <d v="2022-12-28T00:00:00"/>
-    <x v="3"/>
-    <s v="Exited"/>
-    <s v="Other"/>
-    <x v="3"/>
-  </r>
-  <r>
-    <n v="1090"/>
-    <s v="HR"/>
-    <d v="2020-12-15T00:00:00"/>
-    <m/>
-    <x v="0"/>
-    <s v="Active"/>
-    <s v="Other"/>
-    <x v="21"/>
-  </r>
-  <r>
-    <n v="1091"/>
-    <s v="Sales"/>
-    <d v="2020-09-25T00:00:00"/>
-    <m/>
-    <x v="0"/>
-    <s v="Active"/>
-    <s v="Female"/>
-    <x v="22"/>
-  </r>
-  <r>
-    <n v="1092"/>
-    <s v="Sales"/>
-    <d v="2024-12-06T00:00:00"/>
-    <m/>
-    <x v="0"/>
-    <s v="Active"/>
-    <s v="Male"/>
-    <x v="12"/>
-  </r>
-  <r>
-    <n v="1093"/>
-    <s v="HR"/>
-    <d v="2024-01-03T00:00:00"/>
-    <m/>
-    <x v="0"/>
-    <s v="Active"/>
-    <s v="Other"/>
-    <x v="16"/>
-  </r>
-  <r>
-    <n v="1094"/>
-    <s v="Marketing"/>
-    <d v="2022-01-29T00:00:00"/>
-    <m/>
-    <x v="0"/>
-    <s v="Active"/>
-    <s v="Other"/>
-    <x v="23"/>
-  </r>
-  <r>
-    <n v="1095"/>
-    <s v="Customer Support"/>
-    <d v="2023-10-16T00:00:00"/>
-    <m/>
-    <x v="0"/>
-    <s v="Active"/>
-    <s v="Female"/>
-    <x v="18"/>
-  </r>
-  <r>
-    <n v="1096"/>
-    <s v="Customer Support"/>
-    <d v="2019-06-08T00:00:00"/>
-    <d v="2021-02-01T00:00:00"/>
-    <x v="5"/>
-    <s v="Exited"/>
-    <s v="Other"/>
-    <x v="3"/>
-  </r>
-  <r>
-    <n v="1097"/>
-    <s v="Customer Support"/>
-    <d v="2021-11-14T00:00:00"/>
-    <d v="2024-08-25T00:00:00"/>
-    <x v="5"/>
-    <s v="Exited"/>
-    <s v="Other"/>
-    <x v="24"/>
-  </r>
-  <r>
-    <n v="1098"/>
-    <s v="Finance"/>
-    <d v="2019-08-23T00:00:00"/>
-    <m/>
-    <x v="0"/>
-    <s v="Active"/>
-    <s v="Male"/>
-    <x v="8"/>
-  </r>
-  <r>
-    <n v="1099"/>
-    <s v="Sales"/>
-    <d v="2024-09-05T00:00:00"/>
-    <m/>
-    <x v="0"/>
-    <s v="Active"/>
-    <s v="Male"/>
-    <x v="12"/>
-  </r>
-  <r>
-    <n v="1100"/>
-    <s v="IT"/>
-    <d v="2018-07-16T00:00:00"/>
-    <d v="2022-05-01T00:00:00"/>
-    <x v="4"/>
-    <s v="Exited"/>
-    <s v="Other"/>
-    <x v="13"/>
-  </r>
-</pivotCacheRecords>
-</file>
-
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{0C2C2937-8713-4556-8C0B-A2D87611ACE6}" name="PivotTable6" cacheId="19" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="D13:F30" firstHeaderRow="1" firstDataRow="1" firstDataCol="0"/>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{D36F2D28-A2C4-480E-BC23-DC40BDADA2E8}" name="PivotTable9" cacheId="26" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="D25:E29" firstHeaderRow="1" firstDataRow="1" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
   <pivotFields count="8">
-    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField numFmtId="164" showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
+    <pivotField axis="axisPage" showAll="0">
+      <items count="3">
+        <item x="0"/>
+        <item x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="4">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
     <pivotField showAll="0"/>
   </pivotFields>
+  <rowFields count="1">
+    <field x="6"/>
+  </rowFields>
+  <rowItems count="4">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <pageFields count="1">
+    <pageField fld="5" item="1" hier="-1"/>
+  </pageFields>
+  <dataFields count="1">
+    <dataField name="Count of Employee ID" fld="0" subtotal="count" baseField="6" baseItem="0"/>
+  </dataFields>
+  <formats count="6">
+    <format dxfId="5">
+      <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="4">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+    <format dxfId="3">
+      <pivotArea field="6" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
+    </format>
+    <format dxfId="2">
+      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
+        <references count="1">
+          <reference field="6" count="0"/>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="1">
+      <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="0">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
+    </format>
+  </formats>
   <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
@@ -2518,7 +5705,221 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{86AE79D3-FF56-41F9-B2D0-E26527E49EFC}" name="PivotTable5" cacheId="19" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{0C2C2937-8713-4556-8C0B-A2D87611ACE6}" name="PivotTable6" cacheId="26" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="10" rowHeaderCaption="ageGroup">
+  <location ref="D13:G19" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
+  <pivotFields count="8">
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="164" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisCol" showAll="0">
+      <items count="3">
+        <item x="0"/>
+        <item x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="4">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="7">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="7"/>
+  </rowFields>
+  <rowItems count="5">
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colFields count="1">
+    <field x="5"/>
+  </colFields>
+  <colItems count="3">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Count of Employee ID" fld="0" subtotal="count" baseField="7" baseItem="0"/>
+  </dataFields>
+  <formats count="20">
+    <format dxfId="25">
+      <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="24">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+    <format dxfId="23">
+      <pivotArea type="origin" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="22">
+      <pivotArea field="5" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisCol" fieldPosition="0"/>
+    </format>
+    <format dxfId="21">
+      <pivotArea type="topRight" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="20">
+      <pivotArea field="7" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
+    </format>
+    <format dxfId="19">
+      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
+        <references count="1">
+          <reference field="7" count="4">
+            <x v="1"/>
+            <x v="2"/>
+            <x v="3"/>
+            <x v="4"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="18">
+      <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="17">
+      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
+        <references count="1">
+          <reference field="5" count="0"/>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="16">
+      <pivotArea dataOnly="0" labelOnly="1" grandCol="1" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="15">
+      <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="14">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+    <format dxfId="13">
+      <pivotArea type="origin" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="12">
+      <pivotArea field="5" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisCol" fieldPosition="0"/>
+    </format>
+    <format dxfId="11">
+      <pivotArea type="topRight" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="10">
+      <pivotArea field="7" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
+    </format>
+    <format dxfId="9">
+      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
+        <references count="1">
+          <reference field="7" count="4">
+            <x v="1"/>
+            <x v="2"/>
+            <x v="3"/>
+            <x v="4"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="8">
+      <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="7">
+      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
+        <references count="1">
+          <reference field="5" count="0"/>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="6">
+      <pivotArea dataOnly="0" labelOnly="1" grandCol="1" outline="0" fieldPosition="0"/>
+    </format>
+  </formats>
+  <chartFormats count="3">
+    <chartFormat chart="9" format="2" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="5" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="9" format="3" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="5" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="9" format="4">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="3">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="5" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="7" count="1" selected="0">
+            <x v="3"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{86AE79D3-FF56-41F9-B2D0-E26527E49EFC}" name="PivotTable5" cacheId="26" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="8" rowHeaderCaption="Reason">
   <location ref="D3:E10" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="8">
     <pivotField dataField="1" showAll="0"/>
@@ -2539,7 +5940,17 @@
     </pivotField>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
+    <pivotField showAll="0">
+      <items count="7">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
   </pivotFields>
   <rowFields count="1">
     <field x="4"/>
@@ -2573,6 +5984,41 @@
   <dataFields count="1">
     <dataField name="no of employees" fld="0" subtotal="count" baseField="4" baseItem="0"/>
   </dataFields>
+  <formats count="6">
+    <format dxfId="31">
+      <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="30">
+      <pivotArea field="4" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
+    </format>
+    <format dxfId="29">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
+    </format>
+    <format dxfId="28">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+    <format dxfId="27">
+      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
+        <references count="1">
+          <reference field="4" count="0"/>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="26">
+      <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
+    </format>
+  </formats>
+  <chartFormats count="1">
+    <chartFormat chart="5" format="1" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
   <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
@@ -2585,15 +6031,15 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{FED4E128-5012-47E9-B01D-7816F98056D5}" name="pivot department" cacheId="13" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="Department">
-  <location ref="A9:B26" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+<file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{FED4E128-5012-47E9-B01D-7816F98056D5}" name="pivot department" cacheId="31" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="Department">
+  <location ref="A9:B24" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="8">
     <pivotField dataField="1" showAll="0"/>
     <pivotField axis="axisRow" showAll="0">
       <items count="7">
         <item sd="0" x="1"/>
-        <item x="3"/>
+        <item sd="0" x="3"/>
         <item x="5"/>
         <item x="0"/>
         <item x="2"/>
@@ -2618,17 +6064,11 @@
     <field x="1"/>
     <field x="5"/>
   </rowFields>
-  <rowItems count="17">
+  <rowItems count="15">
     <i>
       <x/>
     </i>
     <i>
-      <x v="1"/>
-    </i>
-    <i r="1">
-      <x/>
-    </i>
-    <i r="1">
       <x v="1"/>
     </i>
     <i>
@@ -2689,8 +6129,8 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{A8A06D30-EF24-44D5-822E-3CD2E7529FC3}" name="pivotemployee" cacheId="13" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="status">
+<file path=xl/pivotTables/pivotTable5.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{A8A06D30-EF24-44D5-822E-3CD2E7529FC3}" name="pivotemployee" cacheId="31" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="status">
   <location ref="A2:B5" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="8">
     <pivotField dataField="1" showAll="0"/>
@@ -2728,6 +6168,30 @@
   <dataFields count="1">
     <dataField name="no of employees" fld="0" subtotal="count" baseField="5" baseItem="0"/>
   </dataFields>
+  <formats count="6">
+    <format dxfId="37">
+      <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="36">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+    <format dxfId="35">
+      <pivotArea field="5" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
+    </format>
+    <format dxfId="34">
+      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
+        <references count="1">
+          <reference field="5" count="0"/>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="33">
+      <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="32">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
+    </format>
+  </formats>
   <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
@@ -3042,7 +6506,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H101"/>
+  <dimension ref="A1:J101"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.85546875" style="2" bestFit="1" customWidth="1"/>
@@ -3052,10 +6516,11 @@
     <col min="6" max="6" width="5.85546875" style="2" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="7" style="2" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="4.140625" style="2" bestFit="1" customWidth="1"/>
-    <col min="9" max="16384" width="8.85546875" style="2"/>
+    <col min="9" max="9" width="16.28515625" style="2" customWidth="1"/>
+    <col min="10" max="16384" width="8.85546875" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3080,8 +6545,11 @@
       <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I1" s="2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="2">
         <v>1001</v>
       </c>
@@ -3100,8 +6568,16 @@
       <c r="H2" s="2">
         <v>27</v>
       </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I2" s="24">
+        <f ca="1">TODAY()</f>
+        <v>46190</v>
+      </c>
+      <c r="J2" s="2">
+        <f ca="1">ROUNDUP((I2-C2)/365,1)</f>
+        <v>7.6999999999999993</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="2">
         <v>1002</v>
       </c>
@@ -3121,7 +6597,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="2">
         <v>1003</v>
       </c>
@@ -3141,7 +6617,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" s="2">
         <v>1004</v>
       </c>
@@ -3161,7 +6637,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" s="2">
         <v>1005</v>
       </c>
@@ -3187,7 +6663,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" s="2">
         <v>1006</v>
       </c>
@@ -3213,7 +6689,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" s="2">
         <v>1007</v>
       </c>
@@ -3233,7 +6709,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" s="2">
         <v>1008</v>
       </c>
@@ -3253,7 +6729,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" s="2">
         <v>1009</v>
       </c>
@@ -3273,7 +6749,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" s="2">
         <v>1010</v>
       </c>
@@ -3293,7 +6769,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" s="2">
         <v>1011</v>
       </c>
@@ -3313,7 +6789,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" s="2">
         <v>1012</v>
       </c>
@@ -3339,7 +6815,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" s="2">
         <v>1013</v>
       </c>
@@ -3365,7 +6841,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" s="2">
         <v>1014</v>
       </c>
@@ -3385,7 +6861,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16" s="2">
         <v>1015</v>
       </c>
@@ -5316,347 +8792,407 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4FBFEBF7-E327-4F24-AFA8-CCB4AB4E943C}">
-  <dimension ref="A1:H30"/>
+  <dimension ref="A1:G29"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="19.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="20.42578125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="18.140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="16" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.7109375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="16.5703125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.42578125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="11.140625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.85546875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="7.28515625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="20.42578125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="6.5703125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.42578125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="8.42578125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="5.5703125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="6.140625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="11.42578125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="11.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A1" s="17" t="s">
+    <row r="1" spans="1:7" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="B1" s="13"/>
+    </row>
+    <row r="2" spans="1:7" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="B2" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="B1" s="17"/>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A2" s="13" t="s">
+      <c r="D2" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="E2" s="13"/>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A3" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="B3" s="11">
+        <v>62</v>
+      </c>
+      <c r="D3" s="15" t="s">
+        <v>38</v>
+      </c>
+      <c r="E3" s="16" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="B4" s="11">
+        <v>38</v>
+      </c>
+      <c r="D4" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="E4" s="11">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A5" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="B5" s="11">
+        <v>100</v>
+      </c>
+      <c r="D5" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="E5" s="11">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="D6" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="E6" s="11">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="D7" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="E7" s="11">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A8" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="B8" s="13"/>
+      <c r="D8" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="E8" s="11">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A9" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="B9" t="s">
+        <v>29</v>
+      </c>
+      <c r="D9" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="E9" s="11">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A10" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B10" s="6">
+        <v>24</v>
+      </c>
+      <c r="D10" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="E10" s="11">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B11" s="6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A12" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="B12" s="6">
+        <v>14</v>
+      </c>
+      <c r="D12" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="E12" s="14"/>
+      <c r="F12" s="14"/>
+      <c r="G12" s="13"/>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A13" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="B13" s="6">
+        <v>12</v>
+      </c>
+      <c r="D13" s="17" t="s">
         <v>27</v>
       </c>
-      <c r="B2" t="s">
+      <c r="E13" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="F13" s="9"/>
+      <c r="G13" s="18"/>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A14" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B14" s="6">
+        <v>2</v>
+      </c>
+      <c r="D14" s="17" t="s">
+        <v>39</v>
+      </c>
+      <c r="E14" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="F14" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="G14" s="18" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A15" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B15" s="6">
+        <v>22</v>
+      </c>
+      <c r="D15" s="19" t="s">
+        <v>34</v>
+      </c>
+      <c r="E15" s="11">
+        <v>14</v>
+      </c>
+      <c r="F15" s="11">
+        <v>10</v>
+      </c>
+      <c r="G15" s="20">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A16" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="B16" s="6">
+        <v>12</v>
+      </c>
+      <c r="D16" s="19" t="s">
+        <v>35</v>
+      </c>
+      <c r="E16" s="11">
+        <v>14</v>
+      </c>
+      <c r="F16" s="11">
+        <v>14</v>
+      </c>
+      <c r="G16" s="20">
         <v>28</v>
       </c>
-      <c r="G2" t="s">
-        <v>31</v>
-      </c>
-      <c r="H2" t="s">
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A17" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B17" s="6">
+        <v>10</v>
+      </c>
+      <c r="D17" s="19" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A3" s="14" t="s">
+      <c r="E17" s="11">
         <v>20</v>
       </c>
-      <c r="B3" s="15">
+      <c r="F17" s="11">
+        <v>8</v>
+      </c>
+      <c r="G17" s="20">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A18" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B18" s="6">
+        <v>18</v>
+      </c>
+      <c r="D18" s="19" t="s">
+        <v>33</v>
+      </c>
+      <c r="E18" s="11">
+        <v>14</v>
+      </c>
+      <c r="F18" s="11">
+        <v>6</v>
+      </c>
+      <c r="G18" s="20">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="B19" s="6">
+        <v>8</v>
+      </c>
+      <c r="D19" s="21" t="s">
+        <v>26</v>
+      </c>
+      <c r="E19" s="22">
         <v>62</v>
       </c>
-      <c r="D3" s="13" t="s">
+      <c r="F19" s="22">
+        <v>38</v>
+      </c>
+      <c r="G19" s="23">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A20" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B20" s="6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="B21" s="6">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A22" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="B22" s="6">
+        <v>8</v>
+      </c>
+      <c r="D22" s="12" t="s">
+        <v>41</v>
+      </c>
+      <c r="E22" s="13"/>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A23" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B23" s="6">
+        <v>4</v>
+      </c>
+      <c r="D23" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="E23" s="9" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A24" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="B24" s="6">
+        <v>100</v>
+      </c>
+      <c r="D24" s="9"/>
+      <c r="E24" s="9"/>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="D25" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="E3" t="s">
-        <v>28</v>
-      </c>
-      <c r="G3" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A4" s="14" t="s">
-        <v>21</v>
-      </c>
-      <c r="B4" s="15">
+      <c r="E25" s="9" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="D26" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="E26" s="11">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="D27" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="E27" s="11">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="D28" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="E28" s="11">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="D29" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="E29" s="11">
         <v>38</v>
       </c>
-      <c r="D4" s="14" t="s">
-        <v>14</v>
-      </c>
-      <c r="E4" s="15">
-        <v>6</v>
-      </c>
-      <c r="G4" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A5" s="14" t="s">
-        <v>26</v>
-      </c>
-      <c r="B5" s="15">
-        <v>100</v>
-      </c>
-      <c r="D5" s="14" t="s">
-        <v>17</v>
-      </c>
-      <c r="E5" s="15">
-        <v>8</v>
-      </c>
-      <c r="G5" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="D6" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="E6" s="15">
-        <v>2</v>
-      </c>
-      <c r="G6" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="D7" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="E7" s="15">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A8" s="17" t="s">
-        <v>30</v>
-      </c>
-      <c r="B8" s="17"/>
-      <c r="D8" s="14" t="s">
-        <v>15</v>
-      </c>
-      <c r="E8" s="15">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A9" s="13" t="s">
-        <v>1</v>
-      </c>
-      <c r="B9" t="s">
-        <v>28</v>
-      </c>
-      <c r="D9" s="14" t="s">
-        <v>16</v>
-      </c>
-      <c r="E9" s="15">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A10" s="14" t="s">
-        <v>9</v>
-      </c>
-      <c r="B10" s="15">
-        <v>24</v>
-      </c>
-      <c r="D10" s="14" t="s">
-        <v>26</v>
-      </c>
-      <c r="E10" s="15">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A11" s="14" t="s">
-        <v>11</v>
-      </c>
-      <c r="B11" s="15">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A12" s="16" t="s">
-        <v>20</v>
-      </c>
-      <c r="B12" s="15">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A13" s="16" t="s">
-        <v>21</v>
-      </c>
-      <c r="B13" s="15">
-        <v>6</v>
-      </c>
-      <c r="D13" s="4"/>
-      <c r="E13" s="5"/>
-      <c r="F13" s="6"/>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A14" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="B14" s="15">
-        <v>14</v>
-      </c>
-      <c r="D14" s="7"/>
-      <c r="E14" s="8"/>
-      <c r="F14" s="9"/>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A15" s="16" t="s">
-        <v>20</v>
-      </c>
-      <c r="B15" s="15">
-        <v>12</v>
-      </c>
-      <c r="D15" s="7"/>
-      <c r="E15" s="8"/>
-      <c r="F15" s="9"/>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A16" s="16" t="s">
-        <v>21</v>
-      </c>
-      <c r="B16" s="15">
-        <v>2</v>
-      </c>
-      <c r="D16" s="7"/>
-      <c r="E16" s="8"/>
-      <c r="F16" s="9"/>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A17" s="14" t="s">
-        <v>8</v>
-      </c>
-      <c r="B17" s="15">
-        <v>22</v>
-      </c>
-      <c r="D17" s="7"/>
-      <c r="E17" s="8"/>
-      <c r="F17" s="9"/>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A18" s="16" t="s">
-        <v>20</v>
-      </c>
-      <c r="B18" s="15">
-        <v>12</v>
-      </c>
-      <c r="D18" s="7"/>
-      <c r="E18" s="8"/>
-      <c r="F18" s="9"/>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A19" s="16" t="s">
-        <v>21</v>
-      </c>
-      <c r="B19" s="15">
-        <v>10</v>
-      </c>
-      <c r="D19" s="7"/>
-      <c r="E19" s="8"/>
-      <c r="F19" s="9"/>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A20" s="14" t="s">
-        <v>10</v>
-      </c>
-      <c r="B20" s="15">
-        <v>18</v>
-      </c>
-      <c r="D20" s="7"/>
-      <c r="E20" s="8"/>
-      <c r="F20" s="9"/>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A21" s="16" t="s">
-        <v>20</v>
-      </c>
-      <c r="B21" s="15">
-        <v>8</v>
-      </c>
-      <c r="D21" s="7"/>
-      <c r="E21" s="8"/>
-      <c r="F21" s="9"/>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A22" s="16" t="s">
-        <v>21</v>
-      </c>
-      <c r="B22" s="15">
-        <v>10</v>
-      </c>
-      <c r="D22" s="7"/>
-      <c r="E22" s="8"/>
-      <c r="F22" s="9"/>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A23" s="14" t="s">
-        <v>12</v>
-      </c>
-      <c r="B23" s="15">
-        <v>12</v>
-      </c>
-      <c r="D23" s="7"/>
-      <c r="E23" s="8"/>
-      <c r="F23" s="9"/>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A24" s="16" t="s">
-        <v>20</v>
-      </c>
-      <c r="B24" s="15">
-        <v>8</v>
-      </c>
-      <c r="D24" s="7"/>
-      <c r="E24" s="8"/>
-      <c r="F24" s="9"/>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A25" s="16" t="s">
-        <v>21</v>
-      </c>
-      <c r="B25" s="15">
-        <v>4</v>
-      </c>
-      <c r="D25" s="7"/>
-      <c r="E25" s="8"/>
-      <c r="F25" s="9"/>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A26" s="14" t="s">
-        <v>26</v>
-      </c>
-      <c r="B26" s="15">
-        <v>100</v>
-      </c>
-      <c r="D26" s="7"/>
-      <c r="E26" s="8"/>
-      <c r="F26" s="9"/>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="D27" s="7"/>
-      <c r="E27" s="8"/>
-      <c r="F27" s="9"/>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="D28" s="7"/>
-      <c r="E28" s="8"/>
-      <c r="F28" s="9"/>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="D29" s="7"/>
-      <c r="E29" s="8"/>
-      <c r="F29" s="9"/>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="D30" s="10"/>
-      <c r="E30" s="11"/>
-      <c r="F30" s="12"/>
     </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="5">
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="A8:B8"/>
+    <mergeCell ref="D2:E2"/>
+    <mergeCell ref="D12:G12"/>
+    <mergeCell ref="D22:E22"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4F7FE185-93F6-4844-BF36-D06A1BBE198C}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
 </file>
--- a/Employee Turnover Analysis Excel Dashboard Dataset.xlsx
+++ b/Employee Turnover Analysis Excel Dashboard Dataset.xlsx
@@ -1,36 +1,42 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30026"/>
-  <workbookPr hidePivotFieldList="1" defaultThemeVersion="124226"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\notes\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39ABD47E-C739-40E3-9615-215997ED9567}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{70CFE260-4FFF-4B59-957A-A4A858AC5E9F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet3" sheetId="3" r:id="rId1"/>
     <sheet name="Sheet1" sheetId="1" r:id="rId2"/>
-    <sheet name="dashboard1" sheetId="2" r:id="rId3"/>
-    <sheet name="Sheet4" sheetId="4" r:id="rId4"/>
+    <sheet name="Sheet5" sheetId="7" r:id="rId3"/>
+    <sheet name="dashboard1" sheetId="2" r:id="rId4"/>
+    <sheet name="dashboard2" sheetId="5" r:id="rId5"/>
+    <sheet name="exit reasons" sheetId="6" r:id="rId6"/>
   </sheets>
   <definedNames>
+    <definedName name="age_wise_record_pivot">dashboard1!$D$13:$F$19</definedName>
     <definedName name="datatable">Sheet1!$A$1:$H$101</definedName>
+    <definedName name="Exited_numbers__gender_pivot">dashboard1!$D$23:$E$29</definedName>
+    <definedName name="Reason_of_switch_Pivot">dashboard1!$D$3:$E$10</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="26" r:id="rId5"/>
-    <pivotCache cacheId="31" r:id="rId6"/>
+    <pivotCache cacheId="2" r:id="rId7"/>
+    <pivotCache cacheId="1" r:id="rId8"/>
+    <pivotCache cacheId="7" r:id="rId9"/>
   </pivotCaches>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="402" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="419" uniqueCount="44">
   <si>
     <t>Employee ID</t>
   </si>
@@ -160,6 +166,9 @@
   <si>
     <t>no of years</t>
   </si>
+  <si>
+    <t>Exit Reasons</t>
+  </si>
 </sst>
 </file>
 
@@ -168,7 +177,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -192,6 +201,22 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -207,7 +232,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="10">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -310,8 +335,8 @@
       <left style="thin">
         <color auto="1"/>
       </left>
-      <right style="thin">
-        <color auto="1"/>
+      <right style="medium">
+        <color indexed="64"/>
       </right>
       <top style="thin">
         <color auto="1"/>
@@ -322,8 +347,8 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color auto="1"/>
+      <left style="medium">
+        <color indexed="64"/>
       </left>
       <right style="medium">
         <color indexed="64"/>
@@ -336,11 +361,27 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -355,7 +396,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
@@ -364,7 +404,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" pivotButton="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -374,27 +418,160 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" pivotButton="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" pivotButton="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" pivotButton="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="38">
+    <dxf>
+      <border>
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <bottom style="medium">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <bottom style="medium">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <bottom style="medium">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <bottom style="medium">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <bottom style="medium">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <bottom style="medium">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <bottom style="medium">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <bottom style="medium">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <bottom style="medium">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <bottom style="medium">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
     <dxf>
       <border>
         <left style="thin">
@@ -529,12 +706,169 @@
     </dxf>
     <dxf>
       <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
         <left style="medium">
           <color indexed="64"/>
         </left>
         <right style="medium">
           <color indexed="64"/>
         </right>
+        <top style="medium">
+          <color indexed="64"/>
+        </top>
         <bottom style="medium">
           <color indexed="64"/>
         </bottom>
@@ -548,6 +882,9 @@
         <right style="medium">
           <color indexed="64"/>
         </right>
+        <top style="medium">
+          <color indexed="64"/>
+        </top>
         <bottom style="medium">
           <color indexed="64"/>
         </bottom>
@@ -561,97 +898,9 @@
         <right style="medium">
           <color indexed="64"/>
         </right>
-        <bottom style="medium">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="medium">
-          <color indexed="64"/>
-        </left>
-        <right style="medium">
-          <color indexed="64"/>
-        </right>
-        <bottom style="medium">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="medium">
-          <color indexed="64"/>
-        </left>
-        <right style="medium">
-          <color indexed="64"/>
-        </right>
-        <bottom style="medium">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="medium">
-          <color indexed="64"/>
-        </left>
-        <right style="medium">
-          <color indexed="64"/>
-        </right>
-        <bottom style="medium">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="medium">
-          <color indexed="64"/>
-        </left>
-        <right style="medium">
-          <color indexed="64"/>
-        </right>
-        <bottom style="medium">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="medium">
-          <color indexed="64"/>
-        </left>
-        <right style="medium">
-          <color indexed="64"/>
-        </right>
-        <bottom style="medium">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="medium">
-          <color indexed="64"/>
-        </left>
-        <right style="medium">
-          <color indexed="64"/>
-        </right>
-        <bottom style="medium">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="medium">
-          <color indexed="64"/>
-        </left>
-        <right style="medium">
-          <color indexed="64"/>
-        </right>
+        <top style="medium">
+          <color indexed="64"/>
+        </top>
         <bottom style="medium">
           <color indexed="64"/>
         </bottom>
@@ -787,208 +1036,6 @@
         <horizontal style="thin">
           <color indexed="64"/>
         </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="medium">
-          <color indexed="64"/>
-        </left>
-        <right style="medium">
-          <color indexed="64"/>
-        </right>
-        <top style="medium">
-          <color indexed="64"/>
-        </top>
-        <bottom style="medium">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="medium">
-          <color indexed="64"/>
-        </left>
-        <right style="medium">
-          <color indexed="64"/>
-        </right>
-        <top style="medium">
-          <color indexed="64"/>
-        </top>
-        <bottom style="medium">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="medium">
-          <color indexed="64"/>
-        </left>
-        <right style="medium">
-          <color indexed="64"/>
-        </right>
-        <top style="medium">
-          <color indexed="64"/>
-        </top>
-        <bottom style="medium">
-          <color indexed="64"/>
-        </bottom>
       </border>
     </dxf>
     <dxf>
@@ -1150,11 +1197,569 @@
     </mc:Fallback>
   </mc:AlternateContent>
   <c:pivotSource>
-    <c:name>[Employee Turnover Analysis Excel Dashboard Dataset.xlsx]dashboard1!PivotTable5</c:name>
-    <c:fmtId val="5"/>
+    <c:name>[Employee Turnover Analysis Excel Dashboard Dataset.xlsx]dashboard1!pivotemployee</c:name>
+    <c:fmtId val="2"/>
   </c:pivotSource>
   <c:chart>
     <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>Employess</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-US" baseline="0"/>
+              <a:t> Exited vs Active</a:t>
+            </a:r>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:pivotFmts>
+      <c:pivotFmt>
+        <c:idx val="0"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln w="19050">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:solidFill>
+              <a:sysClr val="window" lastClr="FFFFFF"/>
+            </a:solidFill>
+            <a:ln>
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000">
+                  <a:lumMod val="25000"/>
+                  <a:lumOff val="75000"/>
+                </a:sysClr>
+              </a:solidFill>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="dk1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:dLblPos val="outEnd"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="1"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="1"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+              <c15:spPr xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
+                <a:prstGeom prst="wedgeRectCallout">
+                  <a:avLst/>
+                </a:prstGeom>
+                <a:noFill/>
+                <a:ln>
+                  <a:noFill/>
+                </a:ln>
+              </c15:spPr>
+            </c:ext>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="1"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln w="19050">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:solidFill>
+              <a:sysClr val="window" lastClr="FFFFFF"/>
+            </a:solidFill>
+            <a:ln>
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000">
+                  <a:lumMod val="25000"/>
+                  <a:lumOff val="75000"/>
+                </a:sysClr>
+              </a:solidFill>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="dk1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:dLblPos val="outEnd"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="1"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="1"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+              <c15:spPr xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
+                <a:prstGeom prst="wedgeRectCallout">
+                  <a:avLst/>
+                </a:prstGeom>
+                <a:noFill/>
+                <a:ln>
+                  <a:noFill/>
+                </a:ln>
+              </c15:spPr>
+            </c:ext>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="2"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln w="19050">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="3"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln w="19050">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+      </c:pivotFmt>
+    </c:pivotFmts>
+    <c:plotArea>
+      <c:layout>
+        <c:manualLayout>
+          <c:layoutTarget val="inner"/>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="0.46904053659959172"/>
+          <c:y val="0.22854280630568649"/>
+          <c:w val="0.46238188976377953"/>
+          <c:h val="0.60392722244785535"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:pieChart>
+        <c:varyColors val="1"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>dashboard1!$B$2</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Total</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:dPt>
+            <c:idx val="0"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000001-3933-4B6B-90A8-0C30CE578061}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="1"/>
+            <c:bubble3D val="0"/>
+            <c:explosion val="11"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000003-3933-4B6B-90A8-0C30CE578061}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dLbls>
+            <c:spPr>
+              <a:solidFill>
+                <a:sysClr val="window" lastClr="FFFFFF"/>
+              </a:solidFill>
+              <a:ln>
+                <a:solidFill>
+                  <a:sysClr val="windowText" lastClr="000000">
+                    <a:lumMod val="25000"/>
+                    <a:lumOff val="75000"/>
+                  </a:sysClr>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="dk1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="outEnd"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="1"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="1"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:spPr xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
+                  <a:prstGeom prst="wedgeRectCallout">
+                    <a:avLst/>
+                  </a:prstGeom>
+                  <a:noFill/>
+                  <a:ln>
+                    <a:noFill/>
+                  </a:ln>
+                </c15:spPr>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>dashboard1!$A$3:$A$5</c:f>
+              <c:strCache>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>Active</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Exited</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>dashboard1!$B$3:$B$5</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>62</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>38</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000004-3933-4B6B-90A8-0C30CE578061}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:showLeaderLines val="0"/>
+        </c:dLbls>
+        <c:firstSliceAng val="0"/>
+      </c:pieChart>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="l"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+  <c:extLst>
+    <c:ext xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" uri="{781A3756-C4B2-4CAC-9D66-4F8BD8637D16}">
+      <c14:pivotOptions>
+        <c14:dropZoneFilter val="1"/>
+        <c14:dropZoneCategories val="1"/>
+        <c14:dropZoneSeries val="1"/>
+        <c14:dropZonesVisible val="1"/>
+      </c14:pivotOptions>
+    </c:ext>
+    <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{E28EC0CA-F0BB-4C9C-879D-F8772B89E7AC}">
+      <c16:pivotOptions16>
+        <c16:showExpandCollapseFieldButtons val="1"/>
+      </c16:pivotOptions16>
+    </c:ext>
+  </c:extLst>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:pivotSource>
+    <c:name>[Employee Turnover Analysis Excel Dashboard Dataset.xlsx]dashboard1!PivotTable5</c:name>
+    <c:fmtId val="16"/>
+  </c:pivotSource>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-IN"/>
+              <a:t>Exit Reasons</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -1298,6 +1903,62 @@
           </c:extLst>
         </c:dLbl>
       </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="2"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
     </c:pivotFmts>
     <c:plotArea>
       <c:layout/>
@@ -1384,7 +2045,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-1E5F-4519-B2A4-08C27588F528}"/>
+              <c16:uniqueId val="{00000000-2652-4FE5-B2A3-2F6BA296D6A9}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1398,18 +2059,18 @@
         </c:dLbls>
         <c:gapWidth val="219"/>
         <c:overlap val="-27"/>
-        <c:axId val="1451795727"/>
-        <c:axId val="1451781807"/>
+        <c:axId val="1380305183"/>
+        <c:axId val="1380284543"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="1451795727"/>
+        <c:axId val="1380305183"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="b"/>
         <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
+        <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
         <c:spPr>
@@ -1445,7 +2106,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1451781807"/>
+        <c:crossAx val="1380284543"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1453,7 +2114,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="1451781807"/>
+        <c:axId val="1380284543"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1474,7 +2135,7 @@
           </c:spPr>
         </c:majorGridlines>
         <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
+        <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
         <c:spPr>
@@ -1504,10 +2165,541 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1451795727"/>
+        <c:crossAx val="1380305183"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+  <c:extLst>
+    <c:ext xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" uri="{781A3756-C4B2-4CAC-9D66-4F8BD8637D16}">
+      <c14:pivotOptions>
+        <c14:dropZoneFilter val="1"/>
+        <c14:dropZoneCategories val="1"/>
+        <c14:dropZonesVisible val="1"/>
+      </c14:pivotOptions>
+    </c:ext>
+    <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{E28EC0CA-F0BB-4C9C-879D-F8772B89E7AC}">
+      <c16:pivotOptions16>
+        <c16:showExpandCollapseFieldButtons val="1"/>
+      </c16:pivotOptions16>
+    </c:ext>
+  </c:extLst>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:pivotSource>
+    <c:name>[Employee Turnover Analysis Excel Dashboard Dataset.xlsx]dashboard1!PivotTable9</c:name>
+    <c:fmtId val="5"/>
+  </c:pivotSource>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>Gender Wise Exit</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-US" baseline="0"/>
+              <a:t> numbers</a:t>
+            </a:r>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:pivotFmts>
+      <c:pivotFmt>
+        <c:idx val="0"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln w="19050">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:solidFill>
+              <a:sysClr val="window" lastClr="FFFFFF"/>
+            </a:solidFill>
+            <a:ln>
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000">
+                  <a:lumMod val="25000"/>
+                  <a:lumOff val="75000"/>
+                </a:sysClr>
+              </a:solidFill>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="dk1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:dLblPos val="ctr"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="1"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="1"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+              <c15:spPr xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
+                <a:prstGeom prst="wedgeRectCallout">
+                  <a:avLst/>
+                </a:prstGeom>
+                <a:noFill/>
+                <a:ln>
+                  <a:noFill/>
+                </a:ln>
+              </c15:spPr>
+            </c:ext>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="1"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln w="19050">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:solidFill>
+              <a:sysClr val="window" lastClr="FFFFFF"/>
+            </a:solidFill>
+            <a:ln>
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000">
+                  <a:lumMod val="25000"/>
+                  <a:lumOff val="75000"/>
+                </a:sysClr>
+              </a:solidFill>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="dk1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:dLblPos val="ctr"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="1"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="1"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+              <c15:spPr xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
+                <a:prstGeom prst="wedgeRectCallout">
+                  <a:avLst/>
+                </a:prstGeom>
+                <a:noFill/>
+                <a:ln>
+                  <a:noFill/>
+                </a:ln>
+              </c15:spPr>
+            </c:ext>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="2"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln w="19050">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="3"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln w="19050">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="4"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln w="19050">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+      </c:pivotFmt>
+    </c:pivotFmts>
+    <c:plotArea>
+      <c:layout/>
+      <c:pieChart>
+        <c:varyColors val="1"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>dashboard1!$E$25</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Total</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:dPt>
+            <c:idx val="0"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000001-0053-41A3-9DB6-38EAAF43725F}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="1"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000003-0053-41A3-9DB6-38EAAF43725F}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="2"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000005-0053-41A3-9DB6-38EAAF43725F}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dLbls>
+            <c:spPr>
+              <a:solidFill>
+                <a:sysClr val="window" lastClr="FFFFFF"/>
+              </a:solidFill>
+              <a:ln>
+                <a:solidFill>
+                  <a:sysClr val="windowText" lastClr="000000">
+                    <a:lumMod val="25000"/>
+                    <a:lumOff val="75000"/>
+                  </a:sysClr>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="dk1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="ctr"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="1"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="1"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:spPr xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
+                  <a:prstGeom prst="wedgeRectCallout">
+                    <a:avLst/>
+                  </a:prstGeom>
+                  <a:noFill/>
+                  <a:ln>
+                    <a:noFill/>
+                  </a:ln>
+                </c15:spPr>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>dashboard1!$D$26:$D$29</c:f>
+              <c:strCache>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>Female</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Male</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Other</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>dashboard1!$E$26:$E$29</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>22</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000006-0053-41A3-9DB6-38EAAF43725F}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:dLblPos val="ctr"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:showLeaderLines val="0"/>
+        </c:dLbls>
+        <c:firstSliceAng val="0"/>
+      </c:pieChart>
       <c:spPr>
         <a:noFill/>
         <a:ln>
@@ -1560,15 +2752,13 @@
   </c:chart>
   <c:spPr>
     <a:solidFill>
-      <a:schemeClr val="tx2">
-        <a:lumMod val="40000"/>
-        <a:lumOff val="60000"/>
-      </a:schemeClr>
+      <a:schemeClr val="bg1"/>
     </a:solidFill>
     <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
       <a:solidFill>
-        <a:schemeClr val="accent1">
-          <a:lumMod val="75000"/>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
         </a:schemeClr>
       </a:solidFill>
       <a:round/>
@@ -1590,12 +2780,12 @@
     <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
     <c:pageSetup/>
   </c:printSettings>
+  <c:userShapes r:id="rId3"/>
   <c:extLst>
     <c:ext xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" uri="{781A3756-C4B2-4CAC-9D66-4F8BD8637D16}">
       <c14:pivotOptions>
         <c14:dropZoneFilter val="1"/>
         <c14:dropZoneCategories val="1"/>
-        <c14:dropZoneData val="1"/>
         <c14:dropZoneSeries val="1"/>
         <c14:dropZonesVisible val="1"/>
       </c14:pivotOptions>
@@ -1609,7 +2799,7 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="en-US"/>
@@ -1624,9 +2814,64 @@
   </mc:AlternateContent>
   <c:pivotSource>
     <c:name>[Employee Turnover Analysis Excel Dashboard Dataset.xlsx]dashboard1!PivotTable6</c:name>
-    <c:fmtId val="9"/>
+    <c:fmtId val="11"/>
   </c:pivotSource>
   <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>Exited by age</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
     <c:autoTitleDeleted val="0"/>
     <c:pivotFmts>
       <c:pivotFmt>
@@ -1691,11 +2936,8 @@
           <a:solidFill>
             <a:schemeClr val="accent1"/>
           </a:solidFill>
-          <a:ln w="28575" cap="rnd">
-            <a:solidFill>
-              <a:schemeClr val="accent1"/>
-            </a:solidFill>
-            <a:round/>
+          <a:ln>
+            <a:noFill/>
           </a:ln>
           <a:effectLst/>
         </c:spPr>
@@ -1800,76 +3042,6 @@
           </c:extLst>
         </c:dLbl>
       </c:pivotFmt>
-      <c:pivotFmt>
-        <c:idx val="3"/>
-        <c:spPr>
-          <a:ln w="28575" cap="rnd">
-            <a:solidFill>
-              <a:schemeClr val="accent1"/>
-            </a:solidFill>
-            <a:round/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:marker>
-          <c:symbol val="none"/>
-        </c:marker>
-        <c:dLbl>
-          <c:idx val="0"/>
-          <c:spPr>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:txPr>
-            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
-              <a:spAutoFit/>
-            </a:bodyPr>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr>
-                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                  <a:solidFill>
-                    <a:schemeClr val="tx1">
-                      <a:lumMod val="75000"/>
-                      <a:lumOff val="25000"/>
-                    </a:schemeClr>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:pPr>
-              <a:endParaRPr lang="en-US"/>
-            </a:p>
-          </c:txPr>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
-          </c:extLst>
-        </c:dLbl>
-      </c:pivotFmt>
-      <c:pivotFmt>
-        <c:idx val="4"/>
-        <c:spPr>
-          <a:solidFill>
-            <a:schemeClr val="accent3">
-              <a:lumMod val="75000"/>
-            </a:schemeClr>
-          </a:solidFill>
-          <a:ln>
-            <a:noFill/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-      </c:pivotFmt>
     </c:pivotFmts>
     <c:plotArea>
       <c:layout>
@@ -1877,14 +3049,14 @@
           <c:layoutTarget val="inner"/>
           <c:xMode val="edge"/>
           <c:yMode val="edge"/>
-          <c:x val="5.2692038495188102E-2"/>
-          <c:y val="0.20731262758821814"/>
-          <c:w val="0.73580752405949257"/>
-          <c:h val="0.65853091280256637"/>
+          <c:x val="0.17406647533544287"/>
+          <c:y val="0.19285223367697593"/>
+          <c:w val="0.78217028478916772"/>
+          <c:h val="0.72376509637326258"/>
         </c:manualLayout>
       </c:layout>
       <c:barChart>
-        <c:barDir val="col"/>
+        <c:barDir val="bar"/>
         <c:grouping val="clustered"/>
         <c:varyColors val="0"/>
         <c:ser>
@@ -1896,7 +3068,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Active</c:v>
+                  <c:v>Exited</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -1911,27 +3083,6 @@
             <a:effectLst/>
           </c:spPr>
           <c:invertIfNegative val="0"/>
-          <c:dPt>
-            <c:idx val="2"/>
-            <c:invertIfNegative val="0"/>
-            <c:bubble3D val="0"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent3">
-                  <a:lumMod val="75000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:ln>
-                <a:noFill/>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:extLst>
-              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000002-9AA9-4AA7-9FAA-FC3F505C72BC}"/>
-              </c:ext>
-            </c:extLst>
-          </c:dPt>
           <c:cat>
             <c:strRef>
               <c:f>dashboard1!$D$15:$D$19</c:f>
@@ -1959,94 +3110,6 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>14</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>14</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>20</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>14</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-9AA9-4AA7-9FAA-FC3F505C72BC}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:dLbls>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-        </c:dLbls>
-        <c:gapWidth val="150"/>
-        <c:axId val="1451757327"/>
-        <c:axId val="1435022031"/>
-      </c:barChart>
-      <c:lineChart>
-        <c:grouping val="standard"/>
-        <c:varyColors val="0"/>
-        <c:ser>
-          <c:idx val="1"/>
-          <c:order val="1"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>dashboard1!$F$13:$F$14</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>Exited</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="28575" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="accent2"/>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="none"/>
-          </c:marker>
-          <c:cat>
-            <c:strRef>
-              <c:f>dashboard1!$D$15:$D$19</c:f>
-              <c:strCache>
-                <c:ptCount val="4"/>
-                <c:pt idx="0">
-                  <c:v>20-29</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>30-39</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>40-49</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>50-60</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>dashboard1!$F$15:$F$19</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="4"/>
-                <c:pt idx="0">
                   <c:v>10</c:v>
                 </c:pt>
                 <c:pt idx="1">
@@ -2061,10 +3124,9 @@
               </c:numCache>
             </c:numRef>
           </c:val>
-          <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-9AA9-4AA7-9FAA-FC3F505C72BC}"/>
+              <c16:uniqueId val="{00000000-2E8D-4DB7-97F7-CC474201821F}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -2076,18 +3138,17 @@
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
         </c:dLbls>
-        <c:marker val="1"/>
-        <c:smooth val="0"/>
-        <c:axId val="1451757327"/>
-        <c:axId val="1435022031"/>
-      </c:lineChart>
+        <c:gapWidth val="182"/>
+        <c:axId val="1509812463"/>
+        <c:axId val="1509809103"/>
+      </c:barChart>
       <c:catAx>
-        <c:axId val="1451757327"/>
+        <c:axId val="1509812463"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
         <c:delete val="0"/>
-        <c:axPos val="b"/>
+        <c:axPos val="l"/>
         <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
@@ -2125,7 +3186,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1435022031"/>
+        <c:crossAx val="1509809103"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2133,12 +3194,12 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="1435022031"/>
+        <c:axId val="1509809103"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
         <c:delete val="0"/>
-        <c:axPos val="l"/>
+        <c:axPos val="b"/>
         <c:majorGridlines>
           <c:spPr>
             <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
@@ -2184,7 +3245,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1451757327"/>
+        <c:crossAx val="1509812463"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -2196,37 +3257,6 @@
         <a:effectLst/>
       </c:spPr>
     </c:plotArea>
-    <c:legend>
-      <c:legendPos val="r"/>
-      <c:overlay val="0"/>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-      <c:txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:endParaRPr lang="en-US"/>
-        </a:p>
-      </c:txPr>
-    </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
     <c:showDLblsOverMax val="0"/>
@@ -2240,10 +3270,7 @@
   </c:chart>
   <c:spPr>
     <a:solidFill>
-      <a:schemeClr val="tx2">
-        <a:lumMod val="40000"/>
-        <a:lumOff val="60000"/>
-      </a:schemeClr>
+      <a:schemeClr val="bg1"/>
     </a:solidFill>
     <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
       <a:solidFill>
@@ -2276,8 +3303,6 @@
       <c14:pivotOptions>
         <c14:dropZoneFilter val="1"/>
         <c14:dropZoneCategories val="1"/>
-        <c14:dropZoneData val="1"/>
-        <c14:dropZoneSeries val="1"/>
         <c14:dropZonesVisible val="1"/>
       </c14:pivotOptions>
     </c:ext>
@@ -2370,7 +3395,606 @@
 </cs:colorStyle>
 </file>
 
+<file path=xl/charts/colors3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors4.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
 <file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="251">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050">
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="25400">
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
@@ -2873,8 +4497,527 @@
 </cs:chartStyle>
 </file>
 
-<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="322">
+<file path=xl/charts/style3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="251">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050">
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="25400">
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style4.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="216">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
@@ -3199,8 +5342,8 @@
       <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
           <a:schemeClr val="tx1">
-            <a:lumMod val="75000"/>
-            <a:lumOff val="25000"/>
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
           </a:schemeClr>
         </a:solidFill>
         <a:round/>
@@ -3264,17 +5407,6 @@
         <a:lumOff val="35000"/>
       </a:schemeClr>
     </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
     <cs:defRPr sz="900" kern="1200"/>
   </cs:seriesAxis>
   <cs:seriesLine>
@@ -3391,61 +5523,81 @@
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>23</xdr:col>
+      <xdr:colOff>250540</xdr:colOff>
+      <xdr:row>44</xdr:row>
+      <xdr:rowOff>133350</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Picture 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A002B906-E9DD-BF08-9DE8-43A062A3DC9C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="14271340" cy="8515350"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>14287</xdr:rowOff>
+      <xdr:colOff>361950</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>23812</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>304800</xdr:colOff>
-      <xdr:row>15</xdr:row>
-      <xdr:rowOff>90487</xdr:rowOff>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>57150</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>28575</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="3" name="Chart 4">
+        <xdr:cNvPr id="2" name="Chart 1">
+          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1" tooltip="view details"/>
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1701C174-0EF5-E6D9-C9AD-46050C7F3F39}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvGraphicFramePr/>
-      </xdr:nvGraphicFramePr>
-      <xdr:xfrm>
-        <a:off x="0" y="0"/>
-        <a:ext cx="0" cy="0"/>
-      </xdr:xfrm>
-      <a:graphic>
-        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-        </a:graphicData>
-      </a:graphic>
-    </xdr:graphicFrame>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>185737</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>15</xdr:col>
-      <xdr:colOff>304800</xdr:colOff>
-      <xdr:row>15</xdr:row>
-      <xdr:rowOff>71437</xdr:rowOff>
-    </xdr:to>
-    <xdr:graphicFrame macro="">
-      <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="4" name="Chart 5">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6B0040D6-0E2E-F1B5-C1CD-1CA19867CE38}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3125DDA3-4956-16CB-1577-77D025979816}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3464,6 +5616,265 @@
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>161925</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>4762</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>466725</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>80962</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 2">
+          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1" tooltip="View Data"/>
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5F837CF4-1AF4-5EA9-1941-C998DA869A7C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>523875</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>33337</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>533400</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name="Chart 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{605F356E-E696-C90E-ED82-1A2E0CC96F30}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>585787</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>185737</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>19050</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>104775</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="4" name="Chart 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BF773761-1BE8-3880-18CF-DF2603DD1D01}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId4"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>95250</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>85725</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>171450</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>76200</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="5" name="Frame 4">
+          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId5"/>
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B1C48EB7-2C1C-58AB-D378-D313C1C06434}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3752850" y="4181475"/>
+          <a:ext cx="1295400" cy="371475"/>
+        </a:xfrm>
+        <a:prstGeom prst="frame">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent1"/>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="dbl"/>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-IN" sz="1400" b="1" u="sng">
+              <a:solidFill>
+                <a:schemeClr val="accent1">
+                  <a:lumMod val="75000"/>
+                </a:schemeClr>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>View Details</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<c:userShapes xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <cdr:relSizeAnchor xmlns:cdr="http://schemas.openxmlformats.org/drawingml/2006/chartDrawing">
+    <cdr:from>
+      <cdr:x>0.06682</cdr:x>
+      <cdr:y>0.2282</cdr:y>
+    </cdr:from>
+    <cdr:to>
+      <cdr:x>0.21604</cdr:x>
+      <cdr:y>0.45826</cdr:y>
+    </cdr:to>
+    <cdr:sp macro="" textlink="">
+      <cdr:nvSpPr>
+        <cdr:cNvPr id="2" name="Rectangle: Rounded Corners 1">
+          <a:hlinkClick xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+          <a:extLst xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D70C65A0-9745-9CFC-7F46-D0C99F21BA14}"/>
+            </a:ext>
+          </a:extLst>
+        </cdr:cNvPr>
+        <cdr:cNvSpPr/>
+      </cdr:nvSpPr>
+      <cdr:spPr>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:off x="285750" y="585786"/>
+          <a:ext cx="638175" cy="590551"/>
+        </a:xfrm>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="roundRect">
+          <a:avLst/>
+        </a:prstGeom>
+      </cdr:spPr>
+      <cdr:style>
+        <a:lnRef xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </cdr:style>
+      <cdr:txBody>
+        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" vertOverflow="clip"/>
+        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:r>
+            <a:rPr lang="en-IN" sz="1400" kern="1200"/>
+            <a:t>View</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-IN" kern="1200"/>
+            <a:t> </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-IN" sz="1400" kern="1200"/>
+            <a:t>Data</a:t>
+          </a:r>
+        </a:p>
+      </cdr:txBody>
+    </cdr:sp>
+  </cdr:relSizeAnchor>
+</c:userShapes>
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -3606,6 +6017,58 @@
 </pivotCacheDefinition>
 </file>
 
+<file path=xl/pivotCache/pivotCacheDefinition3.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Shalini Rathore" refreshedDate="46191.783794907409" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="100" xr:uid="{93D68D8D-A8BC-4A7F-8C38-8A521403D3BE}">
+  <cacheSource type="worksheet">
+    <worksheetSource ref="A1:I101" sheet="Sheet1"/>
+  </cacheSource>
+  <cacheFields count="9">
+    <cacheField name="Employee ID" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="1001" maxValue="1100"/>
+    </cacheField>
+    <cacheField name="Department" numFmtId="0">
+      <sharedItems count="6">
+        <s v="IT"/>
+        <s v="Customer Support"/>
+        <s v="Marketing"/>
+        <s v="Finance"/>
+        <s v="Sales"/>
+        <s v="HR"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="Join Date" numFmtId="164">
+      <sharedItems containsSemiMixedTypes="0" containsNonDate="0" containsDate="1" containsString="0" minDate="2018-01-23T00:00:00" maxDate="2024-12-07T00:00:00"/>
+    </cacheField>
+    <cacheField name="Exit Date" numFmtId="0">
+      <sharedItems containsNonDate="0" containsDate="1" containsString="0" containsBlank="1" minDate="2020-04-15T00:00:00" maxDate="2024-12-03T00:00:00"/>
+    </cacheField>
+    <cacheField name="Exit Reason" numFmtId="0">
+      <sharedItems containsBlank="1"/>
+    </cacheField>
+    <cacheField name="Status" numFmtId="0">
+      <sharedItems count="2">
+        <s v="Active"/>
+        <s v="Exited"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="Gender" numFmtId="0">
+      <sharedItems/>
+    </cacheField>
+    <cacheField name="Age" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="22" maxValue="53"/>
+    </cacheField>
+    <cacheField name="no of years" numFmtId="0">
+      <sharedItems containsNonDate="0" containsDate="1" containsString="0" containsBlank="1" minDate="2026-06-18T00:00:00" maxDate="2026-06-19T00:00:00"/>
+    </cacheField>
+  </cacheFields>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
+      <x14:pivotCacheDefinition/>
+    </ext>
+  </extLst>
+</pivotCacheDefinition>
+</file>
+
 <file path=xl/pivotCache/pivotCacheRecords1.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="100">
   <r>
@@ -5616,44 +8079,1193 @@
 </pivotCacheRecords>
 </file>
 
+<file path=xl/pivotCache/pivotCacheRecords3.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="100">
+  <r>
+    <n v="1001"/>
+    <x v="0"/>
+    <d v="2018-11-03T00:00:00"/>
+    <m/>
+    <m/>
+    <x v="0"/>
+    <s v="Female"/>
+    <n v="27"/>
+    <d v="2026-06-18T00:00:00"/>
+  </r>
+  <r>
+    <n v="1002"/>
+    <x v="1"/>
+    <d v="2020-10-17T00:00:00"/>
+    <m/>
+    <m/>
+    <x v="0"/>
+    <s v="Female"/>
+    <n v="22"/>
+    <m/>
+  </r>
+  <r>
+    <n v="1003"/>
+    <x v="1"/>
+    <d v="2021-08-15T00:00:00"/>
+    <m/>
+    <m/>
+    <x v="0"/>
+    <s v="Male"/>
+    <n v="50"/>
+    <m/>
+  </r>
+  <r>
+    <n v="1004"/>
+    <x v="1"/>
+    <d v="2023-06-10T00:00:00"/>
+    <m/>
+    <m/>
+    <x v="0"/>
+    <s v="Male"/>
+    <n v="24"/>
+    <m/>
+  </r>
+  <r>
+    <n v="1005"/>
+    <x v="1"/>
+    <d v="2019-01-14T00:00:00"/>
+    <d v="2021-09-10T00:00:00"/>
+    <s v="Better Opportunity"/>
+    <x v="1"/>
+    <s v="Female"/>
+    <n v="50"/>
+    <m/>
+  </r>
+  <r>
+    <n v="1006"/>
+    <x v="2"/>
+    <d v="2022-07-07T00:00:00"/>
+    <d v="2023-02-15T00:00:00"/>
+    <s v="Retirement"/>
+    <x v="1"/>
+    <s v="Female"/>
+    <n v="28"/>
+    <m/>
+  </r>
+  <r>
+    <n v="1007"/>
+    <x v="3"/>
+    <d v="2024-06-14T00:00:00"/>
+    <m/>
+    <m/>
+    <x v="0"/>
+    <s v="Female"/>
+    <n v="40"/>
+    <m/>
+  </r>
+  <r>
+    <n v="1008"/>
+    <x v="0"/>
+    <d v="2018-07-23T00:00:00"/>
+    <m/>
+    <m/>
+    <x v="0"/>
+    <s v="Other"/>
+    <n v="32"/>
+    <m/>
+  </r>
+  <r>
+    <n v="1009"/>
+    <x v="1"/>
+    <d v="2023-03-02T00:00:00"/>
+    <m/>
+    <m/>
+    <x v="0"/>
+    <s v="Other"/>
+    <n v="50"/>
+    <m/>
+  </r>
+  <r>
+    <n v="1010"/>
+    <x v="4"/>
+    <d v="2024-02-04T00:00:00"/>
+    <m/>
+    <m/>
+    <x v="0"/>
+    <s v="Female"/>
+    <n v="24"/>
+    <m/>
+  </r>
+  <r>
+    <n v="1011"/>
+    <x v="5"/>
+    <d v="2024-07-01T00:00:00"/>
+    <m/>
+    <m/>
+    <x v="0"/>
+    <s v="Male"/>
+    <n v="36"/>
+    <m/>
+  </r>
+  <r>
+    <n v="1012"/>
+    <x v="3"/>
+    <d v="2021-01-31T00:00:00"/>
+    <d v="2024-01-31T00:00:00"/>
+    <s v="Retirement"/>
+    <x v="1"/>
+    <s v="Other"/>
+    <n v="49"/>
+    <m/>
+  </r>
+  <r>
+    <n v="1013"/>
+    <x v="0"/>
+    <d v="2018-12-12T00:00:00"/>
+    <d v="2020-04-15T00:00:00"/>
+    <s v="Termination"/>
+    <x v="1"/>
+    <s v="Male"/>
+    <n v="43"/>
+    <m/>
+  </r>
+  <r>
+    <n v="1014"/>
+    <x v="1"/>
+    <d v="2024-01-23T00:00:00"/>
+    <m/>
+    <m/>
+    <x v="0"/>
+    <s v="Male"/>
+    <n v="40"/>
+    <m/>
+  </r>
+  <r>
+    <n v="1015"/>
+    <x v="1"/>
+    <d v="2018-01-23T00:00:00"/>
+    <m/>
+    <m/>
+    <x v="0"/>
+    <s v="Other"/>
+    <n v="42"/>
+    <m/>
+  </r>
+  <r>
+    <n v="1016"/>
+    <x v="0"/>
+    <d v="2019-09-09T00:00:00"/>
+    <d v="2022-04-26T00:00:00"/>
+    <s v="Health Issues"/>
+    <x v="1"/>
+    <s v="Other"/>
+    <n v="35"/>
+    <m/>
+  </r>
+  <r>
+    <n v="1017"/>
+    <x v="3"/>
+    <d v="2019-03-10T00:00:00"/>
+    <d v="2020-10-13T00:00:00"/>
+    <s v="Termination"/>
+    <x v="1"/>
+    <s v="Female"/>
+    <n v="31"/>
+    <m/>
+  </r>
+  <r>
+    <n v="1018"/>
+    <x v="5"/>
+    <d v="2022-02-27T00:00:00"/>
+    <m/>
+    <m/>
+    <x v="0"/>
+    <s v="Other"/>
+    <n v="51"/>
+    <m/>
+  </r>
+  <r>
+    <n v="1019"/>
+    <x v="0"/>
+    <d v="2024-07-12T00:00:00"/>
+    <m/>
+    <m/>
+    <x v="0"/>
+    <s v="Other"/>
+    <n v="48"/>
+    <m/>
+  </r>
+  <r>
+    <n v="1020"/>
+    <x v="3"/>
+    <d v="2019-05-03T00:00:00"/>
+    <d v="2022-12-01T00:00:00"/>
+    <s v="Relocation"/>
+    <x v="1"/>
+    <s v="Female"/>
+    <n v="41"/>
+    <m/>
+  </r>
+  <r>
+    <n v="1021"/>
+    <x v="5"/>
+    <d v="2021-02-23T00:00:00"/>
+    <d v="2024-04-10T00:00:00"/>
+    <s v="Retirement"/>
+    <x v="1"/>
+    <s v="Other"/>
+    <n v="35"/>
+    <m/>
+  </r>
+  <r>
+    <n v="1022"/>
+    <x v="2"/>
+    <d v="2023-11-14T00:00:00"/>
+    <d v="2024-06-03T00:00:00"/>
+    <s v="Health Issues"/>
+    <x v="1"/>
+    <s v="Other"/>
+    <n v="24"/>
+    <m/>
+  </r>
+  <r>
+    <n v="1023"/>
+    <x v="1"/>
+    <d v="2023-11-26T00:00:00"/>
+    <m/>
+    <m/>
+    <x v="0"/>
+    <s v="Other"/>
+    <n v="41"/>
+    <m/>
+  </r>
+  <r>
+    <n v="1024"/>
+    <x v="2"/>
+    <d v="2024-06-22T00:00:00"/>
+    <m/>
+    <m/>
+    <x v="0"/>
+    <s v="Other"/>
+    <n v="40"/>
+    <m/>
+  </r>
+  <r>
+    <n v="1025"/>
+    <x v="0"/>
+    <d v="2019-05-12T00:00:00"/>
+    <m/>
+    <m/>
+    <x v="0"/>
+    <s v="Female"/>
+    <n v="48"/>
+    <m/>
+  </r>
+  <r>
+    <n v="1026"/>
+    <x v="1"/>
+    <d v="2022-11-01T00:00:00"/>
+    <m/>
+    <m/>
+    <x v="0"/>
+    <s v="Female"/>
+    <n v="52"/>
+    <m/>
+  </r>
+  <r>
+    <n v="1027"/>
+    <x v="4"/>
+    <d v="2020-06-24T00:00:00"/>
+    <d v="2021-09-24T00:00:00"/>
+    <s v="Personal Reasons"/>
+    <x v="1"/>
+    <s v="Other"/>
+    <n v="33"/>
+    <m/>
+  </r>
+  <r>
+    <n v="1028"/>
+    <x v="2"/>
+    <d v="2023-06-18T00:00:00"/>
+    <m/>
+    <m/>
+    <x v="0"/>
+    <s v="Male"/>
+    <n v="51"/>
+    <m/>
+  </r>
+  <r>
+    <n v="1029"/>
+    <x v="0"/>
+    <d v="2021-06-13T00:00:00"/>
+    <d v="2022-07-13T00:00:00"/>
+    <s v="Termination"/>
+    <x v="1"/>
+    <s v="Male"/>
+    <n v="46"/>
+    <m/>
+  </r>
+  <r>
+    <n v="1030"/>
+    <x v="2"/>
+    <d v="2018-11-15T00:00:00"/>
+    <d v="2021-04-17T00:00:00"/>
+    <s v="Better Opportunity"/>
+    <x v="1"/>
+    <s v="Other"/>
+    <n v="53"/>
+    <m/>
+  </r>
+  <r>
+    <n v="1031"/>
+    <x v="5"/>
+    <d v="2021-02-22T00:00:00"/>
+    <m/>
+    <m/>
+    <x v="0"/>
+    <s v="Male"/>
+    <n v="35"/>
+    <m/>
+  </r>
+  <r>
+    <n v="1032"/>
+    <x v="0"/>
+    <d v="2024-08-29T00:00:00"/>
+    <m/>
+    <m/>
+    <x v="0"/>
+    <s v="Male"/>
+    <n v="32"/>
+    <m/>
+  </r>
+  <r>
+    <n v="1033"/>
+    <x v="5"/>
+    <d v="2021-06-30T00:00:00"/>
+    <m/>
+    <m/>
+    <x v="0"/>
+    <s v="Female"/>
+    <n v="46"/>
+    <m/>
+  </r>
+  <r>
+    <n v="1034"/>
+    <x v="0"/>
+    <d v="2020-09-14T00:00:00"/>
+    <m/>
+    <m/>
+    <x v="0"/>
+    <s v="Male"/>
+    <n v="50"/>
+    <m/>
+  </r>
+  <r>
+    <n v="1035"/>
+    <x v="2"/>
+    <d v="2018-09-30T00:00:00"/>
+    <d v="2022-09-21T00:00:00"/>
+    <s v="Retirement"/>
+    <x v="1"/>
+    <s v="Male"/>
+    <n v="32"/>
+    <m/>
+  </r>
+  <r>
+    <n v="1036"/>
+    <x v="2"/>
+    <d v="2018-08-02T00:00:00"/>
+    <m/>
+    <m/>
+    <x v="0"/>
+    <s v="Other"/>
+    <n v="29"/>
+    <m/>
+  </r>
+  <r>
+    <n v="1037"/>
+    <x v="2"/>
+    <d v="2021-08-10T00:00:00"/>
+    <d v="2024-12-02T00:00:00"/>
+    <s v="Better Opportunity"/>
+    <x v="1"/>
+    <s v="Other"/>
+    <n v="27"/>
+    <m/>
+  </r>
+  <r>
+    <n v="1038"/>
+    <x v="4"/>
+    <d v="2021-05-08T00:00:00"/>
+    <d v="2023-05-30T00:00:00"/>
+    <s v="Health Issues"/>
+    <x v="1"/>
+    <s v="Female"/>
+    <n v="31"/>
+    <m/>
+  </r>
+  <r>
+    <n v="1039"/>
+    <x v="0"/>
+    <d v="2019-02-17T00:00:00"/>
+    <d v="2022-12-28T00:00:00"/>
+    <s v="Termination"/>
+    <x v="1"/>
+    <s v="Other"/>
+    <n v="24"/>
+    <m/>
+  </r>
+  <r>
+    <n v="1040"/>
+    <x v="5"/>
+    <d v="2020-12-15T00:00:00"/>
+    <m/>
+    <m/>
+    <x v="0"/>
+    <s v="Other"/>
+    <n v="37"/>
+    <m/>
+  </r>
+  <r>
+    <n v="1041"/>
+    <x v="4"/>
+    <d v="2020-09-25T00:00:00"/>
+    <m/>
+    <m/>
+    <x v="0"/>
+    <s v="Female"/>
+    <n v="23"/>
+    <m/>
+  </r>
+  <r>
+    <n v="1042"/>
+    <x v="4"/>
+    <d v="2024-12-06T00:00:00"/>
+    <m/>
+    <m/>
+    <x v="0"/>
+    <s v="Male"/>
+    <n v="31"/>
+    <m/>
+  </r>
+  <r>
+    <n v="1043"/>
+    <x v="5"/>
+    <d v="2024-01-03T00:00:00"/>
+    <m/>
+    <m/>
+    <x v="0"/>
+    <s v="Other"/>
+    <n v="52"/>
+    <m/>
+  </r>
+  <r>
+    <n v="1044"/>
+    <x v="2"/>
+    <d v="2022-01-29T00:00:00"/>
+    <m/>
+    <m/>
+    <x v="0"/>
+    <s v="Other"/>
+    <n v="25"/>
+    <m/>
+  </r>
+  <r>
+    <n v="1045"/>
+    <x v="1"/>
+    <d v="2023-10-16T00:00:00"/>
+    <m/>
+    <m/>
+    <x v="0"/>
+    <s v="Female"/>
+    <n v="46"/>
+    <m/>
+  </r>
+  <r>
+    <n v="1046"/>
+    <x v="1"/>
+    <d v="2019-06-08T00:00:00"/>
+    <d v="2021-02-01T00:00:00"/>
+    <s v="Relocation"/>
+    <x v="1"/>
+    <s v="Other"/>
+    <n v="24"/>
+    <m/>
+  </r>
+  <r>
+    <n v="1047"/>
+    <x v="1"/>
+    <d v="2021-11-14T00:00:00"/>
+    <d v="2024-08-25T00:00:00"/>
+    <s v="Relocation"/>
+    <x v="1"/>
+    <s v="Other"/>
+    <n v="38"/>
+    <m/>
+  </r>
+  <r>
+    <n v="1048"/>
+    <x v="3"/>
+    <d v="2019-08-23T00:00:00"/>
+    <m/>
+    <m/>
+    <x v="0"/>
+    <s v="Male"/>
+    <n v="49"/>
+    <m/>
+  </r>
+  <r>
+    <n v="1049"/>
+    <x v="4"/>
+    <d v="2024-09-05T00:00:00"/>
+    <m/>
+    <m/>
+    <x v="0"/>
+    <s v="Male"/>
+    <n v="31"/>
+    <m/>
+  </r>
+  <r>
+    <n v="1050"/>
+    <x v="0"/>
+    <d v="2018-07-16T00:00:00"/>
+    <d v="2022-05-01T00:00:00"/>
+    <s v="Health Issues"/>
+    <x v="1"/>
+    <s v="Other"/>
+    <n v="51"/>
+    <m/>
+  </r>
+  <r>
+    <n v="1051"/>
+    <x v="0"/>
+    <d v="2018-11-03T00:00:00"/>
+    <m/>
+    <m/>
+    <x v="0"/>
+    <s v="Female"/>
+    <n v="27"/>
+    <m/>
+  </r>
+  <r>
+    <n v="1052"/>
+    <x v="1"/>
+    <d v="2020-10-17T00:00:00"/>
+    <m/>
+    <m/>
+    <x v="0"/>
+    <s v="Female"/>
+    <n v="22"/>
+    <m/>
+  </r>
+  <r>
+    <n v="1053"/>
+    <x v="1"/>
+    <d v="2021-08-15T00:00:00"/>
+    <m/>
+    <m/>
+    <x v="0"/>
+    <s v="Male"/>
+    <n v="50"/>
+    <m/>
+  </r>
+  <r>
+    <n v="1054"/>
+    <x v="1"/>
+    <d v="2023-06-10T00:00:00"/>
+    <m/>
+    <m/>
+    <x v="0"/>
+    <s v="Male"/>
+    <n v="24"/>
+    <m/>
+  </r>
+  <r>
+    <n v="1055"/>
+    <x v="1"/>
+    <d v="2019-01-14T00:00:00"/>
+    <d v="2021-09-10T00:00:00"/>
+    <s v="Better Opportunity"/>
+    <x v="1"/>
+    <s v="Female"/>
+    <n v="50"/>
+    <m/>
+  </r>
+  <r>
+    <n v="1056"/>
+    <x v="2"/>
+    <d v="2022-07-07T00:00:00"/>
+    <d v="2023-02-15T00:00:00"/>
+    <s v="Retirement"/>
+    <x v="1"/>
+    <s v="Female"/>
+    <n v="28"/>
+    <m/>
+  </r>
+  <r>
+    <n v="1057"/>
+    <x v="3"/>
+    <d v="2024-06-14T00:00:00"/>
+    <m/>
+    <m/>
+    <x v="0"/>
+    <s v="Female"/>
+    <n v="40"/>
+    <m/>
+  </r>
+  <r>
+    <n v="1058"/>
+    <x v="0"/>
+    <d v="2018-07-23T00:00:00"/>
+    <m/>
+    <m/>
+    <x v="0"/>
+    <s v="Other"/>
+    <n v="32"/>
+    <m/>
+  </r>
+  <r>
+    <n v="1059"/>
+    <x v="1"/>
+    <d v="2023-03-02T00:00:00"/>
+    <m/>
+    <m/>
+    <x v="0"/>
+    <s v="Other"/>
+    <n v="50"/>
+    <m/>
+  </r>
+  <r>
+    <n v="1060"/>
+    <x v="4"/>
+    <d v="2024-02-04T00:00:00"/>
+    <m/>
+    <m/>
+    <x v="0"/>
+    <s v="Female"/>
+    <n v="24"/>
+    <m/>
+  </r>
+  <r>
+    <n v="1061"/>
+    <x v="5"/>
+    <d v="2024-07-01T00:00:00"/>
+    <m/>
+    <m/>
+    <x v="0"/>
+    <s v="Male"/>
+    <n v="36"/>
+    <m/>
+  </r>
+  <r>
+    <n v="1062"/>
+    <x v="3"/>
+    <d v="2021-01-31T00:00:00"/>
+    <d v="2024-01-31T00:00:00"/>
+    <s v="Retirement"/>
+    <x v="1"/>
+    <s v="Other"/>
+    <n v="49"/>
+    <m/>
+  </r>
+  <r>
+    <n v="1063"/>
+    <x v="0"/>
+    <d v="2018-12-12T00:00:00"/>
+    <d v="2020-04-15T00:00:00"/>
+    <s v="Termination"/>
+    <x v="1"/>
+    <s v="Male"/>
+    <n v="43"/>
+    <m/>
+  </r>
+  <r>
+    <n v="1064"/>
+    <x v="1"/>
+    <d v="2024-01-23T00:00:00"/>
+    <m/>
+    <m/>
+    <x v="0"/>
+    <s v="Male"/>
+    <n v="40"/>
+    <m/>
+  </r>
+  <r>
+    <n v="1065"/>
+    <x v="1"/>
+    <d v="2018-01-23T00:00:00"/>
+    <m/>
+    <m/>
+    <x v="0"/>
+    <s v="Other"/>
+    <n v="42"/>
+    <m/>
+  </r>
+  <r>
+    <n v="1066"/>
+    <x v="0"/>
+    <d v="2019-09-09T00:00:00"/>
+    <d v="2022-04-26T00:00:00"/>
+    <s v="Health Issues"/>
+    <x v="1"/>
+    <s v="Other"/>
+    <n v="35"/>
+    <m/>
+  </r>
+  <r>
+    <n v="1067"/>
+    <x v="3"/>
+    <d v="2019-03-10T00:00:00"/>
+    <d v="2020-10-13T00:00:00"/>
+    <s v="Termination"/>
+    <x v="1"/>
+    <s v="Female"/>
+    <n v="31"/>
+    <m/>
+  </r>
+  <r>
+    <n v="1068"/>
+    <x v="5"/>
+    <d v="2022-02-27T00:00:00"/>
+    <m/>
+    <m/>
+    <x v="0"/>
+    <s v="Other"/>
+    <n v="51"/>
+    <m/>
+  </r>
+  <r>
+    <n v="1069"/>
+    <x v="0"/>
+    <d v="2024-07-12T00:00:00"/>
+    <m/>
+    <m/>
+    <x v="0"/>
+    <s v="Other"/>
+    <n v="48"/>
+    <m/>
+  </r>
+  <r>
+    <n v="1070"/>
+    <x v="3"/>
+    <d v="2019-05-03T00:00:00"/>
+    <d v="2022-12-01T00:00:00"/>
+    <s v="Relocation"/>
+    <x v="1"/>
+    <s v="Female"/>
+    <n v="41"/>
+    <m/>
+  </r>
+  <r>
+    <n v="1071"/>
+    <x v="5"/>
+    <d v="2021-02-23T00:00:00"/>
+    <d v="2024-04-10T00:00:00"/>
+    <s v="Retirement"/>
+    <x v="1"/>
+    <s v="Other"/>
+    <n v="35"/>
+    <m/>
+  </r>
+  <r>
+    <n v="1072"/>
+    <x v="2"/>
+    <d v="2023-11-14T00:00:00"/>
+    <d v="2024-06-03T00:00:00"/>
+    <s v="Health Issues"/>
+    <x v="1"/>
+    <s v="Other"/>
+    <n v="24"/>
+    <m/>
+  </r>
+  <r>
+    <n v="1073"/>
+    <x v="1"/>
+    <d v="2023-11-26T00:00:00"/>
+    <m/>
+    <m/>
+    <x v="0"/>
+    <s v="Other"/>
+    <n v="41"/>
+    <m/>
+  </r>
+  <r>
+    <n v="1074"/>
+    <x v="2"/>
+    <d v="2024-06-22T00:00:00"/>
+    <m/>
+    <m/>
+    <x v="0"/>
+    <s v="Other"/>
+    <n v="40"/>
+    <m/>
+  </r>
+  <r>
+    <n v="1075"/>
+    <x v="0"/>
+    <d v="2019-05-12T00:00:00"/>
+    <m/>
+    <m/>
+    <x v="0"/>
+    <s v="Female"/>
+    <n v="48"/>
+    <m/>
+  </r>
+  <r>
+    <n v="1076"/>
+    <x v="1"/>
+    <d v="2022-11-01T00:00:00"/>
+    <m/>
+    <m/>
+    <x v="0"/>
+    <s v="Female"/>
+    <n v="52"/>
+    <m/>
+  </r>
+  <r>
+    <n v="1077"/>
+    <x v="4"/>
+    <d v="2020-06-24T00:00:00"/>
+    <d v="2021-09-24T00:00:00"/>
+    <s v="Personal Reasons"/>
+    <x v="1"/>
+    <s v="Other"/>
+    <n v="33"/>
+    <m/>
+  </r>
+  <r>
+    <n v="1078"/>
+    <x v="2"/>
+    <d v="2023-06-18T00:00:00"/>
+    <m/>
+    <m/>
+    <x v="0"/>
+    <s v="Male"/>
+    <n v="51"/>
+    <m/>
+  </r>
+  <r>
+    <n v="1079"/>
+    <x v="0"/>
+    <d v="2021-06-13T00:00:00"/>
+    <d v="2022-07-13T00:00:00"/>
+    <s v="Termination"/>
+    <x v="1"/>
+    <s v="Male"/>
+    <n v="46"/>
+    <m/>
+  </r>
+  <r>
+    <n v="1080"/>
+    <x v="2"/>
+    <d v="2018-11-15T00:00:00"/>
+    <d v="2021-04-17T00:00:00"/>
+    <s v="Better Opportunity"/>
+    <x v="1"/>
+    <s v="Other"/>
+    <n v="53"/>
+    <m/>
+  </r>
+  <r>
+    <n v="1081"/>
+    <x v="5"/>
+    <d v="2021-02-22T00:00:00"/>
+    <m/>
+    <m/>
+    <x v="0"/>
+    <s v="Male"/>
+    <n v="35"/>
+    <m/>
+  </r>
+  <r>
+    <n v="1082"/>
+    <x v="0"/>
+    <d v="2024-08-29T00:00:00"/>
+    <m/>
+    <m/>
+    <x v="0"/>
+    <s v="Male"/>
+    <n v="32"/>
+    <m/>
+  </r>
+  <r>
+    <n v="1083"/>
+    <x v="5"/>
+    <d v="2021-06-30T00:00:00"/>
+    <m/>
+    <m/>
+    <x v="0"/>
+    <s v="Female"/>
+    <n v="46"/>
+    <m/>
+  </r>
+  <r>
+    <n v="1084"/>
+    <x v="0"/>
+    <d v="2020-09-14T00:00:00"/>
+    <m/>
+    <m/>
+    <x v="0"/>
+    <s v="Male"/>
+    <n v="50"/>
+    <m/>
+  </r>
+  <r>
+    <n v="1085"/>
+    <x v="2"/>
+    <d v="2018-09-30T00:00:00"/>
+    <d v="2022-09-21T00:00:00"/>
+    <s v="Retirement"/>
+    <x v="1"/>
+    <s v="Male"/>
+    <n v="32"/>
+    <m/>
+  </r>
+  <r>
+    <n v="1086"/>
+    <x v="2"/>
+    <d v="2018-08-02T00:00:00"/>
+    <m/>
+    <m/>
+    <x v="0"/>
+    <s v="Other"/>
+    <n v="29"/>
+    <m/>
+  </r>
+  <r>
+    <n v="1087"/>
+    <x v="2"/>
+    <d v="2021-08-10T00:00:00"/>
+    <d v="2024-12-02T00:00:00"/>
+    <s v="Better Opportunity"/>
+    <x v="1"/>
+    <s v="Other"/>
+    <n v="27"/>
+    <m/>
+  </r>
+  <r>
+    <n v="1088"/>
+    <x v="4"/>
+    <d v="2021-05-08T00:00:00"/>
+    <d v="2023-05-30T00:00:00"/>
+    <s v="Health Issues"/>
+    <x v="1"/>
+    <s v="Female"/>
+    <n v="31"/>
+    <m/>
+  </r>
+  <r>
+    <n v="1089"/>
+    <x v="0"/>
+    <d v="2019-02-17T00:00:00"/>
+    <d v="2022-12-28T00:00:00"/>
+    <s v="Termination"/>
+    <x v="1"/>
+    <s v="Other"/>
+    <n v="24"/>
+    <m/>
+  </r>
+  <r>
+    <n v="1090"/>
+    <x v="5"/>
+    <d v="2020-12-15T00:00:00"/>
+    <m/>
+    <m/>
+    <x v="0"/>
+    <s v="Other"/>
+    <n v="37"/>
+    <m/>
+  </r>
+  <r>
+    <n v="1091"/>
+    <x v="4"/>
+    <d v="2020-09-25T00:00:00"/>
+    <m/>
+    <m/>
+    <x v="0"/>
+    <s v="Female"/>
+    <n v="23"/>
+    <m/>
+  </r>
+  <r>
+    <n v="1092"/>
+    <x v="4"/>
+    <d v="2024-12-06T00:00:00"/>
+    <m/>
+    <m/>
+    <x v="0"/>
+    <s v="Male"/>
+    <n v="31"/>
+    <m/>
+  </r>
+  <r>
+    <n v="1093"/>
+    <x v="5"/>
+    <d v="2024-01-03T00:00:00"/>
+    <m/>
+    <m/>
+    <x v="0"/>
+    <s v="Other"/>
+    <n v="52"/>
+    <m/>
+  </r>
+  <r>
+    <n v="1094"/>
+    <x v="2"/>
+    <d v="2022-01-29T00:00:00"/>
+    <m/>
+    <m/>
+    <x v="0"/>
+    <s v="Other"/>
+    <n v="25"/>
+    <m/>
+  </r>
+  <r>
+    <n v="1095"/>
+    <x v="1"/>
+    <d v="2023-10-16T00:00:00"/>
+    <m/>
+    <m/>
+    <x v="0"/>
+    <s v="Female"/>
+    <n v="46"/>
+    <m/>
+  </r>
+  <r>
+    <n v="1096"/>
+    <x v="1"/>
+    <d v="2019-06-08T00:00:00"/>
+    <d v="2021-02-01T00:00:00"/>
+    <s v="Relocation"/>
+    <x v="1"/>
+    <s v="Other"/>
+    <n v="24"/>
+    <m/>
+  </r>
+  <r>
+    <n v="1097"/>
+    <x v="1"/>
+    <d v="2021-11-14T00:00:00"/>
+    <d v="2024-08-25T00:00:00"/>
+    <s v="Relocation"/>
+    <x v="1"/>
+    <s v="Other"/>
+    <n v="38"/>
+    <m/>
+  </r>
+  <r>
+    <n v="1098"/>
+    <x v="3"/>
+    <d v="2019-08-23T00:00:00"/>
+    <m/>
+    <m/>
+    <x v="0"/>
+    <s v="Male"/>
+    <n v="49"/>
+    <m/>
+  </r>
+  <r>
+    <n v="1099"/>
+    <x v="4"/>
+    <d v="2024-09-05T00:00:00"/>
+    <m/>
+    <m/>
+    <x v="0"/>
+    <s v="Male"/>
+    <n v="31"/>
+    <m/>
+  </r>
+  <r>
+    <n v="1100"/>
+    <x v="0"/>
+    <d v="2018-07-16T00:00:00"/>
+    <d v="2022-05-01T00:00:00"/>
+    <s v="Health Issues"/>
+    <x v="1"/>
+    <s v="Other"/>
+    <n v="51"/>
+    <m/>
+  </r>
+</pivotCacheRecords>
+</file>
+
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{D36F2D28-A2C4-480E-BC23-DC40BDADA2E8}" name="PivotTable9" cacheId="26" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="D25:E29" firstHeaderRow="1" firstDataRow="1" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
-  <pivotFields count="8">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{0FAA966F-6642-4057-9D3B-E33C6152A236}" name="PivotTable1" cacheId="7" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="I2:J19" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="9">
     <pivotField dataField="1" showAll="0"/>
-    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="7">
+        <item sd="0" x="1"/>
+        <item x="3"/>
+        <item x="5"/>
+        <item x="0"/>
+        <item x="2"/>
+        <item x="4"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
     <pivotField numFmtId="164" showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
-    <pivotField axis="axisPage" showAll="0">
+    <pivotField axis="axisRow" showAll="0">
       <items count="3">
         <item x="0"/>
         <item x="1"/>
         <item t="default"/>
       </items>
     </pivotField>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="4">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
     <pivotField showAll="0"/>
   </pivotFields>
-  <rowFields count="1">
-    <field x="6"/>
+  <rowFields count="2">
+    <field x="1"/>
+    <field x="5"/>
   </rowFields>
-  <rowItems count="4">
+  <rowItems count="17">
     <i>
       <x/>
     </i>
     <i>
       <x v="1"/>
     </i>
+    <i r="1">
+      <x/>
+    </i>
+    <i r="1">
+      <x v="1"/>
+    </i>
     <i>
       <x v="2"/>
+    </i>
+    <i r="1">
+      <x/>
+    </i>
+    <i r="1">
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i r="1">
+      <x/>
+    </i>
+    <i r="1">
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i r="1">
+      <x/>
+    </i>
+    <i r="1">
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="5"/>
+    </i>
+    <i r="1">
+      <x/>
+    </i>
+    <i r="1">
+      <x v="1"/>
     </i>
     <i t="grand">
       <x/>
@@ -5662,36 +9274,9 @@
   <colItems count="1">
     <i/>
   </colItems>
-  <pageFields count="1">
-    <pageField fld="5" item="1" hier="-1"/>
-  </pageFields>
   <dataFields count="1">
-    <dataField name="Count of Employee ID" fld="0" subtotal="count" baseField="6" baseItem="0"/>
+    <dataField name="Count of Employee ID" fld="0" subtotal="count" baseField="1" baseItem="0"/>
   </dataFields>
-  <formats count="6">
-    <format dxfId="5">
-      <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
-    </format>
-    <format dxfId="4">
-      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
-    </format>
-    <format dxfId="3">
-      <pivotArea field="6" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
-    </format>
-    <format dxfId="2">
-      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
-        <references count="1">
-          <reference field="6" count="0"/>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="1">
-      <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
-    </format>
-    <format dxfId="0">
-      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
-    </format>
-  </formats>
   <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
@@ -5705,8 +9290,8 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{0C2C2937-8713-4556-8C0B-A2D87611ACE6}" name="PivotTable6" cacheId="26" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="10" rowHeaderCaption="ageGroup">
-  <location ref="D13:G19" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{0C2C2937-8713-4556-8C0B-A2D87611ACE6}" name="PivotTable6" cacheId="2" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="12" rowHeaderCaption="ageGroup">
+  <location ref="D13:F19" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="8">
     <pivotField dataField="1" showAll="0"/>
     <pivotField showAll="0"/>
@@ -5715,7 +9300,7 @@
     <pivotField showAll="0"/>
     <pivotField axis="axisCol" showAll="0">
       <items count="3">
-        <item x="0"/>
+        <item h="1" x="0"/>
         <item x="1"/>
         <item t="default"/>
       </items>
@@ -5763,10 +9348,7 @@
   <colFields count="1">
     <field x="5"/>
   </colFields>
-  <colItems count="3">
-    <i>
-      <x/>
-    </i>
+  <colItems count="2">
     <i>
       <x v="1"/>
     </i>
@@ -5778,25 +9360,25 @@
     <dataField name="Count of Employee ID" fld="0" subtotal="count" baseField="7" baseItem="0"/>
   </dataFields>
   <formats count="20">
-    <format dxfId="25">
+    <format dxfId="19">
       <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="24">
+    <format dxfId="18">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="23">
+    <format dxfId="17">
       <pivotArea type="origin" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="22">
+    <format dxfId="16">
       <pivotArea field="5" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisCol" fieldPosition="0"/>
     </format>
-    <format dxfId="21">
+    <format dxfId="15">
       <pivotArea type="topRight" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="20">
+    <format dxfId="14">
       <pivotArea field="7" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
-    <format dxfId="19">
+    <format dxfId="13">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="7" count="4">
@@ -5808,38 +9390,38 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="18">
+    <format dxfId="12">
       <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="17">
+    <format dxfId="11">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="5" count="0"/>
         </references>
       </pivotArea>
     </format>
-    <format dxfId="16">
+    <format dxfId="10">
       <pivotArea dataOnly="0" labelOnly="1" grandCol="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="15">
+    <format dxfId="9">
       <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="14">
+    <format dxfId="8">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="13">
+    <format dxfId="7">
       <pivotArea type="origin" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="12">
+    <format dxfId="6">
       <pivotArea field="5" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisCol" fieldPosition="0"/>
     </format>
-    <format dxfId="11">
+    <format dxfId="5">
       <pivotArea type="topRight" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="10">
+    <format dxfId="4">
       <pivotArea field="7" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
-    <format dxfId="9">
+    <format dxfId="3">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="7" count="4">
@@ -5851,34 +9433,22 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="8">
+    <format dxfId="2">
       <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="7">
+    <format dxfId="1">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="5" count="0"/>
         </references>
       </pivotArea>
     </format>
-    <format dxfId="6">
+    <format dxfId="0">
       <pivotArea dataOnly="0" labelOnly="1" grandCol="1" outline="0" fieldPosition="0"/>
     </format>
   </formats>
-  <chartFormats count="3">
-    <chartFormat chart="9" format="2" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="5" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="9" format="3" series="1">
+  <chartFormats count="1">
+    <chartFormat chart="11" format="2" series="1">
       <pivotArea type="data" outline="0" fieldPosition="0">
         <references count="2">
           <reference field="4294967294" count="1" selected="0">
@@ -5886,21 +9456,6 @@
           </reference>
           <reference field="5" count="1" selected="0">
             <x v="1"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="9" format="4">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="3">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="5" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="7" count="1" selected="0">
-            <x v="3"/>
           </reference>
         </references>
       </pivotArea>
@@ -5919,7 +9474,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{86AE79D3-FF56-41F9-B2D0-E26527E49EFC}" name="PivotTable5" cacheId="26" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="8" rowHeaderCaption="Reason">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{86AE79D3-FF56-41F9-B2D0-E26527E49EFC}" name="PivotTable5" cacheId="2" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="17" rowHeaderCaption="Reason">
   <location ref="D3:E10" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="8">
     <pivotField dataField="1" showAll="0"/>
@@ -5985,31 +9540,31 @@
     <dataField name="no of employees" fld="0" subtotal="count" baseField="4" baseItem="0"/>
   </dataFields>
   <formats count="6">
-    <format dxfId="31">
+    <format dxfId="25">
       <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="30">
+    <format dxfId="24">
       <pivotArea field="4" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
-    <format dxfId="29">
+    <format dxfId="23">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
     </format>
-    <format dxfId="28">
+    <format dxfId="22">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="27">
+    <format dxfId="21">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="4" count="0"/>
         </references>
       </pivotArea>
     </format>
-    <format dxfId="26">
+    <format dxfId="20">
       <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
     </format>
   </formats>
   <chartFormats count="1">
-    <chartFormat chart="5" format="1" series="1">
+    <chartFormat chart="16" format="2" series="1">
       <pivotArea type="data" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="1" selected="0">
@@ -6032,15 +9587,15 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{FED4E128-5012-47E9-B01D-7816F98056D5}" name="pivot department" cacheId="31" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="Department">
-  <location ref="A9:B24" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{FED4E128-5012-47E9-B01D-7816F98056D5}" name="pivot department" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="Department">
+  <location ref="A9:B22" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="8">
     <pivotField dataField="1" showAll="0"/>
     <pivotField axis="axisRow" showAll="0">
       <items count="7">
         <item sd="0" x="1"/>
         <item sd="0" x="3"/>
-        <item x="5"/>
+        <item sd="0" x="5"/>
         <item x="0"/>
         <item x="2"/>
         <item x="4"/>
@@ -6064,7 +9619,7 @@
     <field x="1"/>
     <field x="5"/>
   </rowFields>
-  <rowItems count="15">
+  <rowItems count="13">
     <i>
       <x/>
     </i>
@@ -6073,12 +9628,6 @@
     </i>
     <i>
       <x v="2"/>
-    </i>
-    <i r="1">
-      <x/>
-    </i>
-    <i r="1">
-      <x v="1"/>
     </i>
     <i>
       <x v="3"/>
@@ -6130,7 +9679,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable5.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{A8A06D30-EF24-44D5-822E-3CD2E7529FC3}" name="pivotemployee" cacheId="31" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="status">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{A8A06D30-EF24-44D5-822E-3CD2E7529FC3}" name="pivotemployee" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="4" rowHeaderCaption="status">
   <location ref="A2:B5" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="8">
     <pivotField dataField="1" showAll="0"/>
@@ -6169,6 +9718,129 @@
     <dataField name="no of employees" fld="0" subtotal="count" baseField="5" baseItem="0"/>
   </dataFields>
   <formats count="6">
+    <format dxfId="31">
+      <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="30">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+    <format dxfId="29">
+      <pivotArea field="5" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
+    </format>
+    <format dxfId="28">
+      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
+        <references count="1">
+          <reference field="5" count="0"/>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="27">
+      <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="26">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
+    </format>
+  </formats>
+  <chartFormats count="3">
+    <chartFormat chart="2" format="1" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="2" format="2">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="5" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="2" format="3">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="5" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable6.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{D36F2D28-A2C4-480E-BC23-DC40BDADA2E8}" name="PivotTable9" cacheId="2" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="7">
+  <location ref="D25:E29" firstHeaderRow="1" firstDataRow="1" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
+  <pivotFields count="8">
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="164" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisPage" showAll="0">
+      <items count="3">
+        <item x="0"/>
+        <item x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="4">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="6"/>
+  </rowFields>
+  <rowItems count="4">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <pageFields count="1">
+    <pageField fld="5" item="1" hier="-1"/>
+  </pageFields>
+  <dataFields count="1">
+    <dataField name="Count of Employee ID" fld="0" subtotal="count" baseField="6" baseItem="0"/>
+  </dataFields>
+  <formats count="6">
     <format dxfId="37">
       <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
     </format>
@@ -6176,12 +9848,12 @@
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
     <format dxfId="35">
-      <pivotArea field="5" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
+      <pivotArea field="6" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
     <format dxfId="34">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
-          <reference field="5" count="0"/>
+          <reference field="6" count="0"/>
         </references>
       </pivotArea>
     </format>
@@ -6192,6 +9864,53 @@
       <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
     </format>
   </formats>
+  <chartFormats count="4">
+    <chartFormat chart="5" format="1" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="5" format="2">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="6" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="5" format="3">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="6" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="5" format="4">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="6" count="1" selected="0">
+            <x v="2"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
   <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
@@ -6568,9 +10287,9 @@
       <c r="H2" s="2">
         <v>27</v>
       </c>
-      <c r="I2" s="24">
+      <c r="I2" s="12">
         <f ca="1">TODAY()</f>
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="J2" s="2">
         <f ca="1">ROUNDUP((I2-C2)/365,1)</f>
@@ -8791,387 +12510,473 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4F77B504-4F0F-4DB8-AD24-4678B9E42983}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4FBFEBF7-E327-4F24-AFA8-CCB4AB4E943C}">
-  <dimension ref="A1:G29"/>
+  <dimension ref="A1:J29"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19.140625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="16" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="20.42578125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="6.5703125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="20.42578125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="16.28515625" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="11.28515625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="11.42578125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="8.42578125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="5.5703125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="19.140625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="20.42578125" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="6.140625" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="11.42578125" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="11.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="12" t="s">
+    <row r="1" spans="1:10" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="B1" s="13"/>
-    </row>
-    <row r="2" spans="1:7" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="8" t="s">
+      <c r="B1" s="14"/>
+    </row>
+    <row r="2" spans="1:10" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="B2" s="9" t="s">
+      <c r="B2" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="D2" s="12" t="s">
+      <c r="D2" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="E2" s="13"/>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="10" t="s">
+      <c r="E2" s="14"/>
+      <c r="I2" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="J2" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A3" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="B3" s="11">
+      <c r="B3" s="8">
         <v>62</v>
       </c>
-      <c r="D3" s="15" t="s">
+      <c r="D3" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="E3" s="16" t="s">
+      <c r="E3" s="11" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" s="10" t="s">
+      <c r="I3" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="J3" s="16">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A4" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="B4" s="11">
+      <c r="B4" s="8">
         <v>38</v>
       </c>
-      <c r="D4" s="10" t="s">
+      <c r="D4" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="E4" s="11">
+      <c r="E4" s="8">
         <v>6</v>
       </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" s="10" t="s">
+      <c r="I4" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="J4" s="16">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A5" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="B5" s="11">
+      <c r="B5" s="8">
         <v>100</v>
       </c>
-      <c r="D5" s="10" t="s">
+      <c r="D5" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="E5" s="11">
+      <c r="E5" s="8">
         <v>8</v>
       </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="D6" s="10" t="s">
+      <c r="I5" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="J5" s="16">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="D6" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="E6" s="11">
+      <c r="E6" s="8">
         <v>2</v>
       </c>
-    </row>
-    <row r="7" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D7" s="10" t="s">
+      <c r="I6" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="J6" s="16">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="D7" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="E7" s="11">
+      <c r="E7" s="8">
         <v>6</v>
       </c>
-    </row>
-    <row r="8" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A8" s="12" t="s">
+      <c r="I7" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="J7" s="16">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A8" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="B8" s="13"/>
-      <c r="D8" s="10" t="s">
+      <c r="B8" s="14"/>
+      <c r="D8" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="E8" s="11">
+      <c r="E8" s="8">
         <v>8</v>
       </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="I8" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="J8" s="16">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
         <v>1</v>
       </c>
       <c r="B9" t="s">
         <v>29</v>
       </c>
-      <c r="D9" s="10" t="s">
+      <c r="D9" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="E9" s="11">
+      <c r="E9" s="8">
         <v>8</v>
       </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="I9" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="J9" s="16">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="B10" s="6">
+      <c r="B10" s="16">
         <v>24</v>
       </c>
-      <c r="D10" s="10" t="s">
+      <c r="D10" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="E10" s="11">
+      <c r="E10" s="8">
         <v>38</v>
       </c>
-    </row>
-    <row r="11" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I10" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="J10" s="16">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="B11" s="6">
+      <c r="B11" s="16">
         <v>10</v>
       </c>
-    </row>
-    <row r="12" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="I11" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="J11" s="16">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="B12" s="6">
+      <c r="B12" s="16">
         <v>14</v>
       </c>
-      <c r="D12" s="12" t="s">
+      <c r="D12" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="E12" s="14"/>
-      <c r="F12" s="14"/>
-      <c r="G12" s="13"/>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A13" s="7" t="s">
+      <c r="E12" s="15"/>
+      <c r="F12" s="15"/>
+      <c r="G12" s="14"/>
+      <c r="I12" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="J12" s="16">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B13" s="16">
+        <v>22</v>
+      </c>
+      <c r="D13" s="21" t="s">
+        <v>27</v>
+      </c>
+      <c r="E13" s="21" t="s">
+        <v>30</v>
+      </c>
+      <c r="F13" s="22"/>
+      <c r="I13" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="J13" s="16">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="B13" s="6">
+      <c r="B14" s="16">
         <v>12</v>
       </c>
-      <c r="D13" s="17" t="s">
+      <c r="D14" s="21" t="s">
+        <v>39</v>
+      </c>
+      <c r="E14" s="22" t="s">
+        <v>21</v>
+      </c>
+      <c r="F14" s="22" t="s">
+        <v>26</v>
+      </c>
+      <c r="I14" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="J14" s="16">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A15" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="B15" s="16">
+        <v>10</v>
+      </c>
+      <c r="D15" s="23" t="s">
+        <v>34</v>
+      </c>
+      <c r="E15" s="19">
+        <v>10</v>
+      </c>
+      <c r="F15" s="17">
+        <v>10</v>
+      </c>
+      <c r="I15" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="J15" s="16">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A16" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B16" s="16">
+        <v>18</v>
+      </c>
+      <c r="D16" s="23" t="s">
+        <v>35</v>
+      </c>
+      <c r="E16" s="19">
+        <v>14</v>
+      </c>
+      <c r="F16" s="17">
+        <v>14</v>
+      </c>
+      <c r="I16" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="J16" s="16">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A17" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="B17" s="16">
+        <v>8</v>
+      </c>
+      <c r="D17" s="23" t="s">
+        <v>36</v>
+      </c>
+      <c r="E17" s="19">
+        <v>8</v>
+      </c>
+      <c r="F17" s="17">
+        <v>8</v>
+      </c>
+      <c r="I17" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="J17" s="16">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="B18" s="16">
+        <v>10</v>
+      </c>
+      <c r="D18" s="24" t="s">
+        <v>33</v>
+      </c>
+      <c r="E18" s="19">
+        <v>6</v>
+      </c>
+      <c r="F18" s="17">
+        <v>6</v>
+      </c>
+      <c r="I18" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="J18" s="16">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="B19" s="16">
+        <v>12</v>
+      </c>
+      <c r="D19" s="24" t="s">
+        <v>26</v>
+      </c>
+      <c r="E19" s="20">
+        <v>38</v>
+      </c>
+      <c r="F19" s="18">
+        <v>38</v>
+      </c>
+      <c r="I19" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="J19" s="16">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A20" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="B20" s="16">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="B21" s="16">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A22" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="B22" s="16">
+        <v>100</v>
+      </c>
+      <c r="D22" s="13" t="s">
+        <v>41</v>
+      </c>
+      <c r="E22" s="14"/>
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="D23" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="E23" s="8" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="D24" s="8"/>
+      <c r="E24" s="8"/>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="D25" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="E25" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="E13" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="F13" s="9"/>
-      <c r="G13" s="18"/>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A14" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="B14" s="6">
-        <v>2</v>
-      </c>
-      <c r="D14" s="17" t="s">
-        <v>39</v>
-      </c>
-      <c r="E14" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="F14" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="G14" s="18" t="s">
+    </row>
+    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="D26" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="E26" s="8">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="D27" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="E27" s="8">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="D28" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="E28" s="8">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="D29" s="9" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A15" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="B15" s="6">
-        <v>22</v>
-      </c>
-      <c r="D15" s="19" t="s">
-        <v>34</v>
-      </c>
-      <c r="E15" s="11">
-        <v>14</v>
-      </c>
-      <c r="F15" s="11">
-        <v>10</v>
-      </c>
-      <c r="G15" s="20">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A16" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="B16" s="6">
-        <v>12</v>
-      </c>
-      <c r="D16" s="19" t="s">
-        <v>35</v>
-      </c>
-      <c r="E16" s="11">
-        <v>14</v>
-      </c>
-      <c r="F16" s="11">
-        <v>14</v>
-      </c>
-      <c r="G16" s="20">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A17" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="B17" s="6">
-        <v>10</v>
-      </c>
-      <c r="D17" s="19" t="s">
-        <v>36</v>
-      </c>
-      <c r="E17" s="11">
-        <v>20</v>
-      </c>
-      <c r="F17" s="11">
-        <v>8</v>
-      </c>
-      <c r="G17" s="20">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A18" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="B18" s="6">
-        <v>18</v>
-      </c>
-      <c r="D18" s="19" t="s">
-        <v>33</v>
-      </c>
-      <c r="E18" s="11">
-        <v>14</v>
-      </c>
-      <c r="F18" s="11">
-        <v>6</v>
-      </c>
-      <c r="G18" s="20">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="B19" s="6">
-        <v>8</v>
-      </c>
-      <c r="D19" s="21" t="s">
-        <v>26</v>
-      </c>
-      <c r="E19" s="22">
-        <v>62</v>
-      </c>
-      <c r="F19" s="22">
-        <v>38</v>
-      </c>
-      <c r="G19" s="23">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A20" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="B20" s="6">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="B21" s="6">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A22" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="B22" s="6">
-        <v>8</v>
-      </c>
-      <c r="D22" s="12" t="s">
-        <v>41</v>
-      </c>
-      <c r="E22" s="13"/>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A23" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="B23" s="6">
-        <v>4</v>
-      </c>
-      <c r="D23" s="8" t="s">
-        <v>5</v>
-      </c>
-      <c r="E23" s="9" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A24" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="B24" s="6">
-        <v>100</v>
-      </c>
-      <c r="D24" s="9"/>
-      <c r="E24" s="9"/>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="D25" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="E25" s="9" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="D26" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="E26" s="11">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="D27" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="E27" s="11">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="D28" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="E28" s="11">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="D29" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="E29" s="11">
+      <c r="E29" s="8">
         <v>38</v>
       </c>
     </row>
@@ -9187,11 +12992,62 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4F7FE185-93F6-4844-BF36-D06A1BBE198C}">
-  <dimension ref="A1"/>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0A3CD709-3FE1-49EF-A208-1E8C06F38C03}">
+  <dimension ref="C14:C16"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
+  <sheetData>
+    <row r="14" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C14" s="27"/>
+    </row>
+    <row r="16" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C16" s="27"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CFFEBE0D-0B57-4060-AE3D-65B48591CFF3}">
+  <dimension ref="A1:L2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A1" s="25"/>
+      <c r="B1" s="25"/>
+      <c r="C1" s="25"/>
+      <c r="D1" s="25"/>
+      <c r="E1" s="25"/>
+      <c r="F1" s="25"/>
+      <c r="G1" s="26" t="s">
+        <v>43</v>
+      </c>
+      <c r="H1" s="26"/>
+      <c r="I1" s="26"/>
+      <c r="J1" s="26"/>
+      <c r="K1" s="26"/>
+      <c r="L1" s="26"/>
+    </row>
+    <row r="2" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A2" s="25"/>
+      <c r="B2" s="25"/>
+      <c r="C2" s="25"/>
+      <c r="D2" s="25"/>
+      <c r="E2" s="25"/>
+      <c r="F2" s="25"/>
+      <c r="G2" s="26"/>
+      <c r="H2" s="26"/>
+      <c r="I2" s="26"/>
+      <c r="J2" s="26"/>
+      <c r="K2" s="26"/>
+      <c r="L2" s="26"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="G1:L2"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>

--- a/Employee Turnover Analysis Excel Dashboard Dataset.xlsx
+++ b/Employee Turnover Analysis Excel Dashboard Dataset.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\notes\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{70CFE260-4FFF-4B59-957A-A4A858AC5E9F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E5ACB52-B659-426E-AEF8-DD04F3690A3C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,9 +16,10 @@
     <sheet name="Sheet3" sheetId="3" r:id="rId1"/>
     <sheet name="Sheet1" sheetId="1" r:id="rId2"/>
     <sheet name="Sheet5" sheetId="7" r:id="rId3"/>
-    <sheet name="dashboard1" sheetId="2" r:id="rId4"/>
-    <sheet name="dashboard2" sheetId="5" r:id="rId5"/>
-    <sheet name="exit reasons" sheetId="6" r:id="rId6"/>
+    <sheet name="Sheet6" sheetId="8" r:id="rId4"/>
+    <sheet name="dashboard1" sheetId="2" r:id="rId5"/>
+    <sheet name="dashboard2" sheetId="5" r:id="rId6"/>
+    <sheet name="exit reasons" sheetId="6" r:id="rId7"/>
   </sheets>
   <definedNames>
     <definedName name="age_wise_record_pivot">dashboard1!$D$13:$F$19</definedName>
@@ -28,9 +29,9 @@
   </definedNames>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="2" r:id="rId7"/>
-    <pivotCache cacheId="1" r:id="rId8"/>
-    <pivotCache cacheId="7" r:id="rId9"/>
+    <pivotCache cacheId="2" r:id="rId8"/>
+    <pivotCache cacheId="1" r:id="rId9"/>
+    <pivotCache cacheId="7" r:id="rId10"/>
   </pivotCaches>
 </workbook>
 </file>
@@ -12520,6 +12521,15 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C651C4B1-600F-409C-93FA-696A6126E827}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4FBFEBF7-E327-4F24-AFA8-CCB4AB4E943C}">
   <dimension ref="A1:J29"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -12992,7 +13002,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0A3CD709-3FE1-49EF-A208-1E8C06F38C03}">
   <dimension ref="C14:C16"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -13009,7 +13019,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CFFEBE0D-0B57-4060-AE3D-65B48591CFF3}">
   <dimension ref="A1:L2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
